--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="122">
   <si>
     <t>Squadra</t>
   </si>
@@ -161,141 +161,6 @@
   </si>
   <si>
     <t>AC Pisa 1909</t>
-  </si>
-  <si>
-    <t>Data</t>
-  </si>
-  <si>
-    <t>Casa</t>
-  </si>
-  <si>
-    <t>Trasferta</t>
-  </si>
-  <si>
-    <t>Giornata</t>
-  </si>
-  <si>
-    <t>2026-08-23 18:30</t>
-  </si>
-  <si>
-    <t>2026-08-30 18:30</t>
-  </si>
-  <si>
-    <t>2026-09-06 18:30</t>
-  </si>
-  <si>
-    <t>2026-09-13 18:30</t>
-  </si>
-  <si>
-    <t>2026-09-20 18:30</t>
-  </si>
-  <si>
-    <t>2026-10-11 18:30</t>
-  </si>
-  <si>
-    <t>2026-10-18 18:30</t>
-  </si>
-  <si>
-    <t>2026-10-25 18:30</t>
-  </si>
-  <si>
-    <t>2026-10-28 18:30</t>
-  </si>
-  <si>
-    <t>2026-11-01 18:30</t>
-  </si>
-  <si>
-    <t>2026-11-08 18:30</t>
-  </si>
-  <si>
-    <t>2026-11-22 18:30</t>
-  </si>
-  <si>
-    <t>2026-11-29 18:30</t>
-  </si>
-  <si>
-    <t>2026-12-06 18:30</t>
-  </si>
-  <si>
-    <t>2026-12-13 18:30</t>
-  </si>
-  <si>
-    <t>2026-12-20 18:30</t>
-  </si>
-  <si>
-    <t>2027-01-03 12:00</t>
-  </si>
-  <si>
-    <t>2027-01-06 12:00</t>
-  </si>
-  <si>
-    <t>2027-01-10 12:00</t>
-  </si>
-  <si>
-    <t>2027-01-17 12:00</t>
-  </si>
-  <si>
-    <t>2027-01-24 12:00</t>
-  </si>
-  <si>
-    <t>2027-01-31 12:00</t>
-  </si>
-  <si>
-    <t>2027-02-07 12:00</t>
-  </si>
-  <si>
-    <t>2027-02-14 12:00</t>
-  </si>
-  <si>
-    <t>2027-02-21 12:00</t>
-  </si>
-  <si>
-    <t>2027-02-28 12:00</t>
-  </si>
-  <si>
-    <t>2027-03-07 12:00</t>
-  </si>
-  <si>
-    <t>2027-03-14 12:00</t>
-  </si>
-  <si>
-    <t>2027-03-21 12:00</t>
-  </si>
-  <si>
-    <t>2027-04-04 12:00</t>
-  </si>
-  <si>
-    <t>2027-04-11 12:00</t>
-  </si>
-  <si>
-    <t>2027-04-18 12:00</t>
-  </si>
-  <si>
-    <t>2027-04-25 12:00</t>
-  </si>
-  <si>
-    <t>2027-05-02 12:00</t>
-  </si>
-  <si>
-    <t>2027-05-09 12:00</t>
-  </si>
-  <si>
-    <t>2027-05-16 12:00</t>
-  </si>
-  <si>
-    <t>2027-05-23 12:00</t>
-  </si>
-  <si>
-    <t>2027-05-30 12:00</t>
-  </si>
-  <si>
-    <t>Frosinone Calcio</t>
-  </si>
-  <si>
-    <t>Venezia FC</t>
-  </si>
-  <si>
-    <t>AC Monza</t>
   </si>
   <si>
     <t>Arsenal FC</t>
@@ -2586,5347 +2451,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D381"/>
+  <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="26" width="18.7109375" customWidth="1"/>
   </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>90</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" t="s">
-        <v>32</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" t="s">
-        <v>88</v>
-      </c>
-      <c r="C8" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" t="s">
-        <v>37</v>
-      </c>
-      <c r="C9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" t="s">
-        <v>89</v>
-      </c>
-      <c r="C10" t="s">
-        <v>42</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>51</v>
-      </c>
-      <c r="B12" t="s">
-        <v>31</v>
-      </c>
-      <c r="C12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>51</v>
-      </c>
-      <c r="B14" t="s">
-        <v>42</v>
-      </c>
-      <c r="C14" t="s">
-        <v>28</v>
-      </c>
-      <c r="D14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" t="s">
-        <v>51</v>
-      </c>
-      <c r="B15" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" t="s">
-        <v>51</v>
-      </c>
-      <c r="B16" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" t="s">
-        <v>26</v>
-      </c>
-      <c r="D16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" t="s">
-        <v>51</v>
-      </c>
-      <c r="B17" t="s">
-        <v>90</v>
-      </c>
-      <c r="C17" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" t="s">
-        <v>51</v>
-      </c>
-      <c r="B18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C18" t="s">
-        <v>89</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="C19" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" t="s">
-        <v>51</v>
-      </c>
-      <c r="B20" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" t="s">
-        <v>88</v>
-      </c>
-      <c r="D20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" t="s">
-        <v>51</v>
-      </c>
-      <c r="B21" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" t="s">
-        <v>33</v>
-      </c>
-      <c r="D21">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" t="s">
-        <v>52</v>
-      </c>
-      <c r="B22" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
-        <v>29</v>
-      </c>
-      <c r="D22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" t="s">
-        <v>52</v>
-      </c>
-      <c r="B23" t="s">
-        <v>39</v>
-      </c>
-      <c r="C23" t="s">
-        <v>42</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4">
-      <c r="A24" t="s">
-        <v>52</v>
-      </c>
-      <c r="B24" t="s">
-        <v>28</v>
-      </c>
-      <c r="C24" t="s">
-        <v>32</v>
-      </c>
-      <c r="D24">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" t="s">
-        <v>52</v>
-      </c>
-      <c r="B25" t="s">
-        <v>37</v>
-      </c>
-      <c r="C25" t="s">
-        <v>90</v>
-      </c>
-      <c r="D25">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="A26" t="s">
-        <v>52</v>
-      </c>
-      <c r="B26" t="s">
-        <v>33</v>
-      </c>
-      <c r="C26" t="s">
-        <v>36</v>
-      </c>
-      <c r="D26">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4">
-      <c r="A27" t="s">
-        <v>52</v>
-      </c>
-      <c r="B27" t="s">
-        <v>26</v>
-      </c>
-      <c r="C27" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4">
-      <c r="A28" t="s">
-        <v>52</v>
-      </c>
-      <c r="B28" t="s">
-        <v>88</v>
-      </c>
-      <c r="C28" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
-      <c r="A29" t="s">
-        <v>52</v>
-      </c>
-      <c r="B29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D29">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4">
-      <c r="A30" t="s">
-        <v>52</v>
-      </c>
-      <c r="B30" t="s">
-        <v>35</v>
-      </c>
-      <c r="C30" t="s">
-        <v>34</v>
-      </c>
-      <c r="D30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4">
-      <c r="A31" t="s">
-        <v>52</v>
-      </c>
-      <c r="B31" t="s">
-        <v>31</v>
-      </c>
-      <c r="C31" t="s">
-        <v>30</v>
-      </c>
-      <c r="D31">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4">
-      <c r="A32" t="s">
-        <v>53</v>
-      </c>
-      <c r="B32" t="s">
-        <v>27</v>
-      </c>
-      <c r="C32" t="s">
-        <v>33</v>
-      </c>
-      <c r="D32">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4">
-      <c r="A33" t="s">
-        <v>53</v>
-      </c>
-      <c r="B33" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4">
-      <c r="A34" t="s">
-        <v>53</v>
-      </c>
-      <c r="B34" t="s">
-        <v>26</v>
-      </c>
-      <c r="C34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D34">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4">
-      <c r="A35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" t="s">
-        <v>29</v>
-      </c>
-      <c r="C35" t="s">
-        <v>37</v>
-      </c>
-      <c r="D35">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4">
-      <c r="A36" t="s">
-        <v>53</v>
-      </c>
-      <c r="B36" t="s">
-        <v>38</v>
-      </c>
-      <c r="C36" t="s">
-        <v>28</v>
-      </c>
-      <c r="D36">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4">
-      <c r="A37" t="s">
-        <v>53</v>
-      </c>
-      <c r="B37" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" t="s">
-        <v>88</v>
-      </c>
-      <c r="D37">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4">
-      <c r="A38" t="s">
-        <v>53</v>
-      </c>
-      <c r="B38" t="s">
-        <v>42</v>
-      </c>
-      <c r="C38" t="s">
-        <v>90</v>
-      </c>
-      <c r="D38">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4">
-      <c r="A39" t="s">
-        <v>53</v>
-      </c>
-      <c r="B39" t="s">
-        <v>89</v>
-      </c>
-      <c r="C39" t="s">
-        <v>40</v>
-      </c>
-      <c r="D39">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4">
-      <c r="A40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" t="s">
-        <v>32</v>
-      </c>
-      <c r="C40" t="s">
-        <v>39</v>
-      </c>
-      <c r="D40">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4">
-      <c r="A41" t="s">
-        <v>53</v>
-      </c>
-      <c r="B41" t="s">
-        <v>36</v>
-      </c>
-      <c r="C41" t="s">
-        <v>31</v>
-      </c>
-      <c r="D41">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4">
-      <c r="A42" t="s">
-        <v>54</v>
-      </c>
-      <c r="B42" t="s">
-        <v>88</v>
-      </c>
-      <c r="C42" t="s">
-        <v>29</v>
-      </c>
-      <c r="D42">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4">
-      <c r="A43" t="s">
-        <v>54</v>
-      </c>
-      <c r="B43" t="s">
-        <v>28</v>
-      </c>
-      <c r="C43" t="s">
-        <v>26</v>
-      </c>
-      <c r="D43">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4">
-      <c r="A44" t="s">
-        <v>54</v>
-      </c>
-      <c r="B44" t="s">
-        <v>89</v>
-      </c>
-      <c r="C44" t="s">
-        <v>34</v>
-      </c>
-      <c r="D44">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4">
-      <c r="A45" t="s">
-        <v>54</v>
-      </c>
-      <c r="B45" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" t="s">
-        <v>32</v>
-      </c>
-      <c r="D45">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4">
-      <c r="A46" t="s">
-        <v>54</v>
-      </c>
-      <c r="B46" t="s">
-        <v>90</v>
-      </c>
-      <c r="C46" t="s">
-        <v>36</v>
-      </c>
-      <c r="D46">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4">
-      <c r="A47" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" t="s">
-        <v>30</v>
-      </c>
-      <c r="C47" t="s">
-        <v>42</v>
-      </c>
-      <c r="D47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4">
-      <c r="A48" t="s">
-        <v>54</v>
-      </c>
-      <c r="B48" t="s">
-        <v>33</v>
-      </c>
-      <c r="C48" t="s">
-        <v>38</v>
-      </c>
-      <c r="D48">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4">
-      <c r="A49" t="s">
-        <v>54</v>
-      </c>
-      <c r="B49" t="s">
-        <v>35</v>
-      </c>
-      <c r="C49" t="s">
-        <v>39</v>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4">
-      <c r="A50" t="s">
-        <v>54</v>
-      </c>
-      <c r="B50" t="s">
-        <v>37</v>
-      </c>
-      <c r="C50" t="s">
-        <v>41</v>
-      </c>
-      <c r="D50">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4">
-      <c r="A51" t="s">
-        <v>54</v>
-      </c>
-      <c r="B51" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" t="s">
-        <v>27</v>
-      </c>
-      <c r="D51">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4">
-      <c r="A52" t="s">
-        <v>55</v>
-      </c>
-      <c r="B52" t="s">
-        <v>32</v>
-      </c>
-      <c r="C52" t="s">
-        <v>89</v>
-      </c>
-      <c r="D52">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4">
-      <c r="A53" t="s">
-        <v>55</v>
-      </c>
-      <c r="B53" t="s">
-        <v>36</v>
-      </c>
-      <c r="C53" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4">
-      <c r="A54" t="s">
-        <v>55</v>
-      </c>
-      <c r="B54" t="s">
-        <v>42</v>
-      </c>
-      <c r="C54" t="s">
-        <v>33</v>
-      </c>
-      <c r="D54">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4">
-      <c r="A55" t="s">
-        <v>55</v>
-      </c>
-      <c r="B55" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" t="s">
-        <v>37</v>
-      </c>
-      <c r="D55">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4">
-      <c r="A56" t="s">
-        <v>55</v>
-      </c>
-      <c r="B56" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4">
-      <c r="A57" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>39</v>
-      </c>
-      <c r="C57" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4">
-      <c r="A58" t="s">
-        <v>55</v>
-      </c>
-      <c r="B58" t="s">
-        <v>29</v>
-      </c>
-      <c r="C58" t="s">
-        <v>28</v>
-      </c>
-      <c r="D58">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="59" spans="1:4">
-      <c r="A59" t="s">
-        <v>55</v>
-      </c>
-      <c r="B59" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" t="s">
-        <v>88</v>
-      </c>
-      <c r="D59">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="60" spans="1:4">
-      <c r="A60" t="s">
-        <v>55</v>
-      </c>
-      <c r="B60" t="s">
-        <v>38</v>
-      </c>
-      <c r="C60" t="s">
-        <v>35</v>
-      </c>
-      <c r="D60">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:4">
-      <c r="A61" t="s">
-        <v>55</v>
-      </c>
-      <c r="B61" t="s">
-        <v>41</v>
-      </c>
-      <c r="C61" t="s">
-        <v>40</v>
-      </c>
-      <c r="D61">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="62" spans="1:4">
-      <c r="A62" t="s">
-        <v>56</v>
-      </c>
-      <c r="B62" t="s">
-        <v>30</v>
-      </c>
-      <c r="C62" t="s">
-        <v>32</v>
-      </c>
-      <c r="D62">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:4">
-      <c r="A63" t="s">
-        <v>56</v>
-      </c>
-      <c r="B63" t="s">
-        <v>31</v>
-      </c>
-      <c r="C63" t="s">
-        <v>34</v>
-      </c>
-      <c r="D63">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:4">
-      <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" t="s">
-        <v>33</v>
-      </c>
-      <c r="C64" t="s">
-        <v>26</v>
-      </c>
-      <c r="D64">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:4">
-      <c r="A65" t="s">
-        <v>56</v>
-      </c>
-      <c r="B65" t="s">
-        <v>28</v>
-      </c>
-      <c r="C65" t="s">
-        <v>41</v>
-      </c>
-      <c r="D65">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:4">
-      <c r="A66" t="s">
-        <v>56</v>
-      </c>
-      <c r="B66" t="s">
-        <v>88</v>
-      </c>
-      <c r="C66" t="s">
-        <v>36</v>
-      </c>
-      <c r="D66">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:4">
-      <c r="A67" t="s">
-        <v>56</v>
-      </c>
-      <c r="B67" t="s">
-        <v>35</v>
-      </c>
-      <c r="C67" t="s">
-        <v>42</v>
-      </c>
-      <c r="D67">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:4">
-      <c r="A68" t="s">
-        <v>56</v>
-      </c>
-      <c r="B68" t="s">
-        <v>89</v>
-      </c>
-      <c r="C68" t="s">
-        <v>27</v>
-      </c>
-      <c r="D68">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:4">
-      <c r="A69" t="s">
-        <v>56</v>
-      </c>
-      <c r="B69" t="s">
-        <v>90</v>
-      </c>
-      <c r="C69" t="s">
-        <v>39</v>
-      </c>
-      <c r="D69">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:4">
-      <c r="A70" t="s">
-        <v>56</v>
-      </c>
-      <c r="B70" t="s">
-        <v>40</v>
-      </c>
-      <c r="C70" t="s">
-        <v>29</v>
-      </c>
-      <c r="D70">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="71" spans="1:4">
-      <c r="A71" t="s">
-        <v>56</v>
-      </c>
-      <c r="B71" t="s">
-        <v>37</v>
-      </c>
-      <c r="C71" t="s">
-        <v>38</v>
-      </c>
-      <c r="D71">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="72" spans="1:4">
-      <c r="A72" t="s">
-        <v>57</v>
-      </c>
-      <c r="B72" t="s">
-        <v>35</v>
-      </c>
-      <c r="C72" t="s">
-        <v>30</v>
-      </c>
-      <c r="D72">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="73" spans="1:4">
-      <c r="A73" t="s">
-        <v>57</v>
-      </c>
-      <c r="B73" t="s">
-        <v>39</v>
-      </c>
-      <c r="C73" t="s">
-        <v>33</v>
-      </c>
-      <c r="D73">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="74" spans="1:4">
-      <c r="A74" t="s">
-        <v>57</v>
-      </c>
-      <c r="B74" t="s">
-        <v>29</v>
-      </c>
-      <c r="C74" t="s">
-        <v>36</v>
-      </c>
-      <c r="D74">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="75" spans="1:4">
-      <c r="A75" t="s">
-        <v>57</v>
-      </c>
-      <c r="B75" t="s">
-        <v>32</v>
-      </c>
-      <c r="C75" t="s">
-        <v>88</v>
-      </c>
-      <c r="D75">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="76" spans="1:4">
-      <c r="A76" t="s">
-        <v>57</v>
-      </c>
-      <c r="B76" t="s">
-        <v>26</v>
-      </c>
-      <c r="C76" t="s">
-        <v>40</v>
-      </c>
-      <c r="D76">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="77" spans="1:4">
-      <c r="A77" t="s">
-        <v>57</v>
-      </c>
-      <c r="B77" t="s">
-        <v>27</v>
-      </c>
-      <c r="C77" t="s">
-        <v>28</v>
-      </c>
-      <c r="D77">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="78" spans="1:4">
-      <c r="A78" t="s">
-        <v>57</v>
-      </c>
-      <c r="B78" t="s">
-        <v>34</v>
-      </c>
-      <c r="C78" t="s">
-        <v>37</v>
-      </c>
-      <c r="D78">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="79" spans="1:4">
-      <c r="A79" t="s">
-        <v>57</v>
-      </c>
-      <c r="B79" t="s">
-        <v>42</v>
-      </c>
-      <c r="C79" t="s">
-        <v>31</v>
-      </c>
-      <c r="D79">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="80" spans="1:4">
-      <c r="A80" t="s">
-        <v>57</v>
-      </c>
-      <c r="B80" t="s">
-        <v>38</v>
-      </c>
-      <c r="C80" t="s">
-        <v>90</v>
-      </c>
-      <c r="D80">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="81" spans="1:4">
-      <c r="A81" t="s">
-        <v>57</v>
-      </c>
-      <c r="B81" t="s">
-        <v>41</v>
-      </c>
-      <c r="C81" t="s">
-        <v>89</v>
-      </c>
-      <c r="D81">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="82" spans="1:4">
-      <c r="A82" t="s">
-        <v>58</v>
-      </c>
-      <c r="B82" t="s">
-        <v>30</v>
-      </c>
-      <c r="C82" t="s">
-        <v>33</v>
-      </c>
-      <c r="D82">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="83" spans="1:4">
-      <c r="A83" t="s">
-        <v>58</v>
-      </c>
-      <c r="B83" t="s">
-        <v>89</v>
-      </c>
-      <c r="C83" t="s">
-        <v>26</v>
-      </c>
-      <c r="D83">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="84" spans="1:4">
-      <c r="A84" t="s">
-        <v>58</v>
-      </c>
-      <c r="B84" t="s">
-        <v>40</v>
-      </c>
-      <c r="C84" t="s">
-        <v>32</v>
-      </c>
-      <c r="D84">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="85" spans="1:4">
-      <c r="A85" t="s">
-        <v>58</v>
-      </c>
-      <c r="B85" t="s">
-        <v>41</v>
-      </c>
-      <c r="C85" t="s">
-        <v>31</v>
-      </c>
-      <c r="D85">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="86" spans="1:4">
-      <c r="A86" t="s">
-        <v>58</v>
-      </c>
-      <c r="B86" t="s">
-        <v>37</v>
-      </c>
-      <c r="C86" t="s">
-        <v>35</v>
-      </c>
-      <c r="D86">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="87" spans="1:4">
-      <c r="A87" t="s">
-        <v>58</v>
-      </c>
-      <c r="B87" t="s">
-        <v>90</v>
-      </c>
-      <c r="C87" t="s">
-        <v>27</v>
-      </c>
-      <c r="D87">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="88" spans="1:4">
-      <c r="A88" t="s">
-        <v>58</v>
-      </c>
-      <c r="B88" t="s">
-        <v>28</v>
-      </c>
-      <c r="C88" t="s">
-        <v>39</v>
-      </c>
-      <c r="D88">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="89" spans="1:4">
-      <c r="A89" t="s">
-        <v>58</v>
-      </c>
-      <c r="B89" t="s">
-        <v>36</v>
-      </c>
-      <c r="C89" t="s">
-        <v>34</v>
-      </c>
-      <c r="D89">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="90" spans="1:4">
-      <c r="A90" t="s">
-        <v>58</v>
-      </c>
-      <c r="B90" t="s">
-        <v>38</v>
-      </c>
-      <c r="C90" t="s">
-        <v>29</v>
-      </c>
-      <c r="D90">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="91" spans="1:4">
-      <c r="A91" t="s">
-        <v>58</v>
-      </c>
-      <c r="B91" t="s">
-        <v>88</v>
-      </c>
-      <c r="C91" t="s">
-        <v>42</v>
-      </c>
-      <c r="D91">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="92" spans="1:4">
-      <c r="A92" t="s">
-        <v>59</v>
-      </c>
-      <c r="B92" t="s">
-        <v>33</v>
-      </c>
-      <c r="C92" t="s">
-        <v>90</v>
-      </c>
-      <c r="D92">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="93" spans="1:4">
-      <c r="A93" t="s">
-        <v>59</v>
-      </c>
-      <c r="B93" t="s">
-        <v>42</v>
-      </c>
-      <c r="C93" t="s">
-        <v>41</v>
-      </c>
-      <c r="D93">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="94" spans="1:4">
-      <c r="A94" t="s">
-        <v>59</v>
-      </c>
-      <c r="B94" t="s">
-        <v>36</v>
-      </c>
-      <c r="C94" t="s">
-        <v>40</v>
-      </c>
-      <c r="D94">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="95" spans="1:4">
-      <c r="A95" t="s">
-        <v>59</v>
-      </c>
-      <c r="B95" t="s">
-        <v>35</v>
-      </c>
-      <c r="C95" t="s">
-        <v>28</v>
-      </c>
-      <c r="D95">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="96" spans="1:4">
-      <c r="A96" t="s">
-        <v>59</v>
-      </c>
-      <c r="B96" t="s">
-        <v>29</v>
-      </c>
-      <c r="C96" t="s">
-        <v>89</v>
-      </c>
-      <c r="D96">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="97" spans="1:4">
-      <c r="A97" t="s">
-        <v>59</v>
-      </c>
-      <c r="B97" t="s">
-        <v>88</v>
-      </c>
-      <c r="C97" t="s">
-        <v>38</v>
-      </c>
-      <c r="D97">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="98" spans="1:4">
-      <c r="A98" t="s">
-        <v>59</v>
-      </c>
-      <c r="B98" t="s">
-        <v>32</v>
-      </c>
-      <c r="C98" t="s">
-        <v>37</v>
-      </c>
-      <c r="D98">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="99" spans="1:4">
-      <c r="A99" t="s">
-        <v>59</v>
-      </c>
-      <c r="B99" t="s">
-        <v>34</v>
-      </c>
-      <c r="C99" t="s">
-        <v>39</v>
-      </c>
-      <c r="D99">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="100" spans="1:4">
-      <c r="A100" t="s">
-        <v>59</v>
-      </c>
-      <c r="B100" t="s">
-        <v>31</v>
-      </c>
-      <c r="C100" t="s">
-        <v>27</v>
-      </c>
-      <c r="D100">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="101" spans="1:4">
-      <c r="A101" t="s">
-        <v>59</v>
-      </c>
-      <c r="B101" t="s">
-        <v>30</v>
-      </c>
-      <c r="C101" t="s">
-        <v>26</v>
-      </c>
-      <c r="D101">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="102" spans="1:4">
-      <c r="A102" t="s">
-        <v>60</v>
-      </c>
-      <c r="B102" t="s">
-        <v>40</v>
-      </c>
-      <c r="C102" t="s">
-        <v>31</v>
-      </c>
-      <c r="D102">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="103" spans="1:4">
-      <c r="A103" t="s">
-        <v>60</v>
-      </c>
-      <c r="B103" t="s">
-        <v>26</v>
-      </c>
-      <c r="C103" t="s">
-        <v>29</v>
-      </c>
-      <c r="D103">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="104" spans="1:4">
-      <c r="A104" t="s">
-        <v>60</v>
-      </c>
-      <c r="B104" t="s">
-        <v>28</v>
-      </c>
-      <c r="C104" t="s">
-        <v>36</v>
-      </c>
-      <c r="D104">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="105" spans="1:4">
-      <c r="A105" t="s">
-        <v>60</v>
-      </c>
-      <c r="B105" t="s">
-        <v>38</v>
-      </c>
-      <c r="C105" t="s">
-        <v>42</v>
-      </c>
-      <c r="D105">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="106" spans="1:4">
-      <c r="A106" t="s">
-        <v>60</v>
-      </c>
-      <c r="B106" t="s">
-        <v>27</v>
-      </c>
-      <c r="C106" t="s">
-        <v>34</v>
-      </c>
-      <c r="D106">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="107" spans="1:4">
-      <c r="A107" t="s">
-        <v>60</v>
-      </c>
-      <c r="B107" t="s">
-        <v>39</v>
-      </c>
-      <c r="C107" t="s">
-        <v>88</v>
-      </c>
-      <c r="D107">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="108" spans="1:4">
-      <c r="A108" t="s">
-        <v>60</v>
-      </c>
-      <c r="B108" t="s">
-        <v>37</v>
-      </c>
-      <c r="C108" t="s">
-        <v>33</v>
-      </c>
-      <c r="D108">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="109" spans="1:4">
-      <c r="A109" t="s">
-        <v>60</v>
-      </c>
-      <c r="B109" t="s">
-        <v>41</v>
-      </c>
-      <c r="C109" t="s">
-        <v>30</v>
-      </c>
-      <c r="D109">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="110" spans="1:4">
-      <c r="A110" t="s">
-        <v>60</v>
-      </c>
-      <c r="B110" t="s">
-        <v>89</v>
-      </c>
-      <c r="C110" t="s">
-        <v>35</v>
-      </c>
-      <c r="D110">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="111" spans="1:4">
-      <c r="A111" t="s">
-        <v>60</v>
-      </c>
-      <c r="B111" t="s">
-        <v>90</v>
-      </c>
-      <c r="C111" t="s">
-        <v>32</v>
-      </c>
-      <c r="D111">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="112" spans="1:4">
-      <c r="A112" t="s">
-        <v>61</v>
-      </c>
-      <c r="B112" t="s">
-        <v>90</v>
-      </c>
-      <c r="C112" t="s">
-        <v>40</v>
-      </c>
-      <c r="D112">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="113" spans="1:4">
-      <c r="A113" t="s">
-        <v>61</v>
-      </c>
-      <c r="B113" t="s">
-        <v>32</v>
-      </c>
-      <c r="C113" t="s">
-        <v>26</v>
-      </c>
-      <c r="D113">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="114" spans="1:4">
-      <c r="A114" t="s">
-        <v>61</v>
-      </c>
-      <c r="B114" t="s">
-        <v>31</v>
-      </c>
-      <c r="C114" t="s">
-        <v>89</v>
-      </c>
-      <c r="D114">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="115" spans="1:4">
-      <c r="A115" t="s">
-        <v>61</v>
-      </c>
-      <c r="B115" t="s">
-        <v>33</v>
-      </c>
-      <c r="C115" t="s">
-        <v>35</v>
-      </c>
-      <c r="D115">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="116" spans="1:4">
-      <c r="A116" t="s">
-        <v>61</v>
-      </c>
-      <c r="B116" t="s">
-        <v>30</v>
-      </c>
-      <c r="C116" t="s">
-        <v>88</v>
-      </c>
-      <c r="D116">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="117" spans="1:4">
-      <c r="A117" t="s">
-        <v>61</v>
-      </c>
-      <c r="B117" t="s">
-        <v>36</v>
-      </c>
-      <c r="C117" t="s">
-        <v>41</v>
-      </c>
-      <c r="D117">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="118" spans="1:4">
-      <c r="A118" t="s">
-        <v>61</v>
-      </c>
-      <c r="B118" t="s">
-        <v>29</v>
-      </c>
-      <c r="C118" t="s">
-        <v>39</v>
-      </c>
-      <c r="D118">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="119" spans="1:4">
-      <c r="A119" t="s">
-        <v>61</v>
-      </c>
-      <c r="B119" t="s">
-        <v>37</v>
-      </c>
-      <c r="C119" t="s">
-        <v>28</v>
-      </c>
-      <c r="D119">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="120" spans="1:4">
-      <c r="A120" t="s">
-        <v>61</v>
-      </c>
-      <c r="B120" t="s">
-        <v>27</v>
-      </c>
-      <c r="C120" t="s">
-        <v>38</v>
-      </c>
-      <c r="D120">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="121" spans="1:4">
-      <c r="A121" t="s">
-        <v>61</v>
-      </c>
-      <c r="B121" t="s">
-        <v>34</v>
-      </c>
-      <c r="C121" t="s">
-        <v>42</v>
-      </c>
-      <c r="D121">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="122" spans="1:4">
-      <c r="A122" t="s">
-        <v>62</v>
-      </c>
-      <c r="B122" t="s">
-        <v>36</v>
-      </c>
-      <c r="C122" t="s">
-        <v>27</v>
-      </c>
-      <c r="D122">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="123" spans="1:4">
-      <c r="A123" t="s">
-        <v>62</v>
-      </c>
-      <c r="B123" t="s">
-        <v>39</v>
-      </c>
-      <c r="C123" t="s">
-        <v>30</v>
-      </c>
-      <c r="D123">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="124" spans="1:4">
-      <c r="A124" t="s">
-        <v>62</v>
-      </c>
-      <c r="B124" t="s">
-        <v>29</v>
-      </c>
-      <c r="C124" t="s">
-        <v>31</v>
-      </c>
-      <c r="D124">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="125" spans="1:4">
-      <c r="A125" t="s">
-        <v>62</v>
-      </c>
-      <c r="B125" t="s">
-        <v>28</v>
-      </c>
-      <c r="C125" t="s">
-        <v>90</v>
-      </c>
-      <c r="D125">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="126" spans="1:4">
-      <c r="A126" t="s">
-        <v>62</v>
-      </c>
-      <c r="B126" t="s">
-        <v>88</v>
-      </c>
-      <c r="C126" t="s">
-        <v>37</v>
-      </c>
-      <c r="D126">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="127" spans="1:4">
-      <c r="A127" t="s">
-        <v>62</v>
-      </c>
-      <c r="B127" t="s">
-        <v>38</v>
-      </c>
-      <c r="C127" t="s">
-        <v>34</v>
-      </c>
-      <c r="D127">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="128" spans="1:4">
-      <c r="A128" t="s">
-        <v>62</v>
-      </c>
-      <c r="B128" t="s">
-        <v>89</v>
-      </c>
-      <c r="C128" t="s">
-        <v>33</v>
-      </c>
-      <c r="D128">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="129" spans="1:4">
-      <c r="A129" t="s">
-        <v>62</v>
-      </c>
-      <c r="B129" t="s">
-        <v>42</v>
-      </c>
-      <c r="C129" t="s">
-        <v>32</v>
-      </c>
-      <c r="D129">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="130" spans="1:4">
-      <c r="A130" t="s">
-        <v>62</v>
-      </c>
-      <c r="B130" t="s">
-        <v>35</v>
-      </c>
-      <c r="C130" t="s">
-        <v>40</v>
-      </c>
-      <c r="D130">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="131" spans="1:4">
-      <c r="A131" t="s">
-        <v>62</v>
-      </c>
-      <c r="B131" t="s">
-        <v>26</v>
-      </c>
-      <c r="C131" t="s">
-        <v>41</v>
-      </c>
-      <c r="D131">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="132" spans="1:4">
-      <c r="A132" t="s">
-        <v>63</v>
-      </c>
-      <c r="B132" t="s">
-        <v>41</v>
-      </c>
-      <c r="C132" t="s">
-        <v>38</v>
-      </c>
-      <c r="D132">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="133" spans="1:4">
-      <c r="A133" t="s">
-        <v>63</v>
-      </c>
-      <c r="B133" t="s">
-        <v>31</v>
-      </c>
-      <c r="C133" t="s">
-        <v>35</v>
-      </c>
-      <c r="D133">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="134" spans="1:4">
-      <c r="A134" t="s">
-        <v>63</v>
-      </c>
-      <c r="B134" t="s">
-        <v>88</v>
-      </c>
-      <c r="C134" t="s">
-        <v>26</v>
-      </c>
-      <c r="D134">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="135" spans="1:4">
-      <c r="A135" t="s">
-        <v>63</v>
-      </c>
-      <c r="B135" t="s">
-        <v>33</v>
-      </c>
-      <c r="C135" t="s">
-        <v>28</v>
-      </c>
-      <c r="D135">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="136" spans="1:4">
-      <c r="A136" t="s">
-        <v>63</v>
-      </c>
-      <c r="B136" t="s">
-        <v>40</v>
-      </c>
-      <c r="C136" t="s">
-        <v>39</v>
-      </c>
-      <c r="D136">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="137" spans="1:4">
-      <c r="A137" t="s">
-        <v>63</v>
-      </c>
-      <c r="B137" t="s">
-        <v>34</v>
-      </c>
-      <c r="C137" t="s">
-        <v>32</v>
-      </c>
-      <c r="D137">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="138" spans="1:4">
-      <c r="A138" t="s">
-        <v>63</v>
-      </c>
-      <c r="B138" t="s">
-        <v>30</v>
-      </c>
-      <c r="C138" t="s">
-        <v>37</v>
-      </c>
-      <c r="D138">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="139" spans="1:4">
-      <c r="A139" t="s">
-        <v>63</v>
-      </c>
-      <c r="B139" t="s">
-        <v>89</v>
-      </c>
-      <c r="C139" t="s">
-        <v>36</v>
-      </c>
-      <c r="D139">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="140" spans="1:4">
-      <c r="A140" t="s">
-        <v>63</v>
-      </c>
-      <c r="B140" t="s">
-        <v>90</v>
-      </c>
-      <c r="C140" t="s">
-        <v>29</v>
-      </c>
-      <c r="D140">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="141" spans="1:4">
-      <c r="A141" t="s">
-        <v>63</v>
-      </c>
-      <c r="B141" t="s">
-        <v>27</v>
-      </c>
-      <c r="C141" t="s">
-        <v>42</v>
-      </c>
-      <c r="D141">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="142" spans="1:4">
-      <c r="A142" t="s">
-        <v>64</v>
-      </c>
-      <c r="B142" t="s">
-        <v>27</v>
-      </c>
-      <c r="C142" t="s">
-        <v>30</v>
-      </c>
-      <c r="D142">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="143" spans="1:4">
-      <c r="A143" t="s">
-        <v>64</v>
-      </c>
-      <c r="B143" t="s">
-        <v>29</v>
-      </c>
-      <c r="C143" t="s">
-        <v>33</v>
-      </c>
-      <c r="D143">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="144" spans="1:4">
-      <c r="A144" t="s">
-        <v>64</v>
-      </c>
-      <c r="B144" t="s">
-        <v>35</v>
-      </c>
-      <c r="C144" t="s">
-        <v>88</v>
-      </c>
-      <c r="D144">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4">
-      <c r="A145" t="s">
-        <v>64</v>
-      </c>
-      <c r="B145" t="s">
-        <v>42</v>
-      </c>
-      <c r="C145" t="s">
-        <v>36</v>
-      </c>
-      <c r="D145">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4">
-      <c r="A146" t="s">
-        <v>64</v>
-      </c>
-      <c r="B146" t="s">
-        <v>37</v>
-      </c>
-      <c r="C146" t="s">
-        <v>40</v>
-      </c>
-      <c r="D146">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4">
-      <c r="A147" t="s">
-        <v>64</v>
-      </c>
-      <c r="B147" t="s">
-        <v>39</v>
-      </c>
-      <c r="C147" t="s">
-        <v>89</v>
-      </c>
-      <c r="D147">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4">
-      <c r="A148" t="s">
-        <v>64</v>
-      </c>
-      <c r="B148" t="s">
-        <v>26</v>
-      </c>
-      <c r="C148" t="s">
-        <v>38</v>
-      </c>
-      <c r="D148">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4">
-      <c r="A149" t="s">
-        <v>64</v>
-      </c>
-      <c r="B149" t="s">
-        <v>31</v>
-      </c>
-      <c r="C149" t="s">
-        <v>90</v>
-      </c>
-      <c r="D149">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4">
-      <c r="A150" t="s">
-        <v>64</v>
-      </c>
-      <c r="B150" t="s">
-        <v>32</v>
-      </c>
-      <c r="C150" t="s">
-        <v>41</v>
-      </c>
-      <c r="D150">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4">
-      <c r="A151" t="s">
-        <v>64</v>
-      </c>
-      <c r="B151" t="s">
-        <v>34</v>
-      </c>
-      <c r="C151" t="s">
-        <v>28</v>
-      </c>
-      <c r="D151">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4">
-      <c r="A152" t="s">
-        <v>65</v>
-      </c>
-      <c r="B152" t="s">
-        <v>30</v>
-      </c>
-      <c r="C152" t="s">
-        <v>29</v>
-      </c>
-      <c r="D152">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4">
-      <c r="A153" t="s">
-        <v>65</v>
-      </c>
-      <c r="B153" t="s">
-        <v>36</v>
-      </c>
-      <c r="C153" t="s">
-        <v>37</v>
-      </c>
-      <c r="D153">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="154" spans="1:4">
-      <c r="A154" t="s">
-        <v>65</v>
-      </c>
-      <c r="B154" t="s">
-        <v>28</v>
-      </c>
-      <c r="C154" t="s">
-        <v>31</v>
-      </c>
-      <c r="D154">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="155" spans="1:4">
-      <c r="A155" t="s">
-        <v>65</v>
-      </c>
-      <c r="B155" t="s">
-        <v>88</v>
-      </c>
-      <c r="C155" t="s">
-        <v>34</v>
-      </c>
-      <c r="D155">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="156" spans="1:4">
-      <c r="A156" t="s">
-        <v>65</v>
-      </c>
-      <c r="B156" t="s">
-        <v>32</v>
-      </c>
-      <c r="C156" t="s">
-        <v>27</v>
-      </c>
-      <c r="D156">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="157" spans="1:4">
-      <c r="A157" t="s">
-        <v>65</v>
-      </c>
-      <c r="B157" t="s">
-        <v>40</v>
-      </c>
-      <c r="C157" t="s">
-        <v>33</v>
-      </c>
-      <c r="D157">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="158" spans="1:4">
-      <c r="A158" t="s">
-        <v>65</v>
-      </c>
-      <c r="B158" t="s">
-        <v>41</v>
-      </c>
-      <c r="C158" t="s">
-        <v>35</v>
-      </c>
-      <c r="D158">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="159" spans="1:4">
-      <c r="A159" t="s">
-        <v>65</v>
-      </c>
-      <c r="B159" t="s">
-        <v>42</v>
-      </c>
-      <c r="C159" t="s">
-        <v>26</v>
-      </c>
-      <c r="D159">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="160" spans="1:4">
-      <c r="A160" t="s">
-        <v>65</v>
-      </c>
-      <c r="B160" t="s">
-        <v>38</v>
-      </c>
-      <c r="C160" t="s">
-        <v>39</v>
-      </c>
-      <c r="D160">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="161" spans="1:4">
-      <c r="A161" t="s">
-        <v>65</v>
-      </c>
-      <c r="B161" t="s">
-        <v>89</v>
-      </c>
-      <c r="C161" t="s">
-        <v>90</v>
-      </c>
-      <c r="D161">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="162" spans="1:4">
-      <c r="A162" t="s">
-        <v>66</v>
-      </c>
-      <c r="B162" t="s">
-        <v>35</v>
-      </c>
-      <c r="C162" t="s">
-        <v>32</v>
-      </c>
-      <c r="D162">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="163" spans="1:4">
-      <c r="A163" t="s">
-        <v>66</v>
-      </c>
-      <c r="B163" t="s">
-        <v>29</v>
-      </c>
-      <c r="C163" t="s">
-        <v>42</v>
-      </c>
-      <c r="D163">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="164" spans="1:4">
-      <c r="A164" t="s">
-        <v>66</v>
-      </c>
-      <c r="B164" t="s">
-        <v>28</v>
-      </c>
-      <c r="C164" t="s">
-        <v>88</v>
-      </c>
-      <c r="D164">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="165" spans="1:4">
-      <c r="A165" t="s">
-        <v>66</v>
-      </c>
-      <c r="B165" t="s">
-        <v>37</v>
-      </c>
-      <c r="C165" t="s">
-        <v>27</v>
-      </c>
-      <c r="D165">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="166" spans="1:4">
-      <c r="A166" t="s">
-        <v>66</v>
-      </c>
-      <c r="B166" t="s">
-        <v>39</v>
-      </c>
-      <c r="C166" t="s">
-        <v>41</v>
-      </c>
-      <c r="D166">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="167" spans="1:4">
-      <c r="A167" t="s">
-        <v>66</v>
-      </c>
-      <c r="B167" t="s">
-        <v>38</v>
-      </c>
-      <c r="C167" t="s">
-        <v>89</v>
-      </c>
-      <c r="D167">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="168" spans="1:4">
-      <c r="A168" t="s">
-        <v>66</v>
-      </c>
-      <c r="B168" t="s">
-        <v>90</v>
-      </c>
-      <c r="C168" t="s">
-        <v>30</v>
-      </c>
-      <c r="D168">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="169" spans="1:4">
-      <c r="A169" t="s">
-        <v>66</v>
-      </c>
-      <c r="B169" t="s">
-        <v>26</v>
-      </c>
-      <c r="C169" t="s">
-        <v>36</v>
-      </c>
-      <c r="D169">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="170" spans="1:4">
-      <c r="A170" t="s">
-        <v>66</v>
-      </c>
-      <c r="B170" t="s">
-        <v>33</v>
-      </c>
-      <c r="C170" t="s">
-        <v>31</v>
-      </c>
-      <c r="D170">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="171" spans="1:4">
-      <c r="A171" t="s">
-        <v>66</v>
-      </c>
-      <c r="B171" t="s">
-        <v>40</v>
-      </c>
-      <c r="C171" t="s">
-        <v>34</v>
-      </c>
-      <c r="D171">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="172" spans="1:4">
-      <c r="A172" t="s">
-        <v>67</v>
-      </c>
-      <c r="B172" t="s">
-        <v>88</v>
-      </c>
-      <c r="C172" t="s">
-        <v>33</v>
-      </c>
-      <c r="D172">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="173" spans="1:4">
-      <c r="A173" t="s">
-        <v>67</v>
-      </c>
-      <c r="B173" t="s">
-        <v>36</v>
-      </c>
-      <c r="C173" t="s">
-        <v>35</v>
-      </c>
-      <c r="D173">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="174" spans="1:4">
-      <c r="A174" t="s">
-        <v>67</v>
-      </c>
-      <c r="B174" t="s">
-        <v>41</v>
-      </c>
-      <c r="C174" t="s">
-        <v>90</v>
-      </c>
-      <c r="D174">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="175" spans="1:4">
-      <c r="A175" t="s">
-        <v>67</v>
-      </c>
-      <c r="B175" t="s">
-        <v>89</v>
-      </c>
-      <c r="C175" t="s">
-        <v>28</v>
-      </c>
-      <c r="D175">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="176" spans="1:4">
-      <c r="A176" t="s">
-        <v>67</v>
-      </c>
-      <c r="B176" t="s">
-        <v>27</v>
-      </c>
-      <c r="C176" t="s">
-        <v>39</v>
-      </c>
-      <c r="D176">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="177" spans="1:4">
-      <c r="A177" t="s">
-        <v>67</v>
-      </c>
-      <c r="B177" t="s">
-        <v>30</v>
-      </c>
-      <c r="C177" t="s">
-        <v>40</v>
-      </c>
-      <c r="D177">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="178" spans="1:4">
-      <c r="A178" t="s">
-        <v>67</v>
-      </c>
-      <c r="B178" t="s">
-        <v>31</v>
-      </c>
-      <c r="C178" t="s">
-        <v>38</v>
-      </c>
-      <c r="D178">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="179" spans="1:4">
-      <c r="A179" t="s">
-        <v>67</v>
-      </c>
-      <c r="B179" t="s">
-        <v>32</v>
-      </c>
-      <c r="C179" t="s">
-        <v>29</v>
-      </c>
-      <c r="D179">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="180" spans="1:4">
-      <c r="A180" t="s">
-        <v>67</v>
-      </c>
-      <c r="B180" t="s">
-        <v>34</v>
-      </c>
-      <c r="C180" t="s">
-        <v>26</v>
-      </c>
-      <c r="D180">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="181" spans="1:4">
-      <c r="A181" t="s">
-        <v>67</v>
-      </c>
-      <c r="B181" t="s">
-        <v>42</v>
-      </c>
-      <c r="C181" t="s">
-        <v>37</v>
-      </c>
-      <c r="D181">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="182" spans="1:4">
-      <c r="A182" t="s">
-        <v>68</v>
-      </c>
-      <c r="B182" t="s">
-        <v>40</v>
-      </c>
-      <c r="C182" t="s">
-        <v>42</v>
-      </c>
-      <c r="D182">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="183" spans="1:4">
-      <c r="A183" t="s">
-        <v>68</v>
-      </c>
-      <c r="B183" t="s">
-        <v>35</v>
-      </c>
-      <c r="C183" t="s">
-        <v>27</v>
-      </c>
-      <c r="D183">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="184" spans="1:4">
-      <c r="A184" t="s">
-        <v>68</v>
-      </c>
-      <c r="B184" t="s">
-        <v>38</v>
-      </c>
-      <c r="C184" t="s">
-        <v>32</v>
-      </c>
-      <c r="D184">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="185" spans="1:4">
-      <c r="A185" t="s">
-        <v>68</v>
-      </c>
-      <c r="B185" t="s">
-        <v>90</v>
-      </c>
-      <c r="C185" t="s">
-        <v>88</v>
-      </c>
-      <c r="D185">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="186" spans="1:4">
-      <c r="A186" t="s">
-        <v>68</v>
-      </c>
-      <c r="B186" t="s">
-        <v>26</v>
-      </c>
-      <c r="C186" t="s">
-        <v>31</v>
-      </c>
-      <c r="D186">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="187" spans="1:4">
-      <c r="A187" t="s">
-        <v>68</v>
-      </c>
-      <c r="B187" t="s">
-        <v>37</v>
-      </c>
-      <c r="C187" t="s">
-        <v>89</v>
-      </c>
-      <c r="D187">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="188" spans="1:4">
-      <c r="A188" t="s">
-        <v>68</v>
-      </c>
-      <c r="B188" t="s">
-        <v>33</v>
-      </c>
-      <c r="C188" t="s">
-        <v>41</v>
-      </c>
-      <c r="D188">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="189" spans="1:4">
-      <c r="A189" t="s">
-        <v>68</v>
-      </c>
-      <c r="B189" t="s">
-        <v>39</v>
-      </c>
-      <c r="C189" t="s">
-        <v>36</v>
-      </c>
-      <c r="D189">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="190" spans="1:4">
-      <c r="A190" t="s">
-        <v>68</v>
-      </c>
-      <c r="B190" t="s">
-        <v>29</v>
-      </c>
-      <c r="C190" t="s">
-        <v>34</v>
-      </c>
-      <c r="D190">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="191" spans="1:4">
-      <c r="A191" t="s">
-        <v>68</v>
-      </c>
-      <c r="B191" t="s">
-        <v>28</v>
-      </c>
-      <c r="C191" t="s">
-        <v>30</v>
-      </c>
-      <c r="D191">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="192" spans="1:4">
-      <c r="A192" t="s">
-        <v>69</v>
-      </c>
-      <c r="B192" t="s">
-        <v>30</v>
-      </c>
-      <c r="C192" t="s">
-        <v>38</v>
-      </c>
-      <c r="D192">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="193" spans="1:4">
-      <c r="A193" t="s">
-        <v>69</v>
-      </c>
-      <c r="B193" t="s">
-        <v>37</v>
-      </c>
-      <c r="C193" t="s">
-        <v>26</v>
-      </c>
-      <c r="D193">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="194" spans="1:4">
-      <c r="A194" t="s">
-        <v>69</v>
-      </c>
-      <c r="B194" t="s">
-        <v>31</v>
-      </c>
-      <c r="C194" t="s">
-        <v>41</v>
-      </c>
-      <c r="D194">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="195" spans="1:4">
-      <c r="A195" t="s">
-        <v>69</v>
-      </c>
-      <c r="B195" t="s">
-        <v>42</v>
-      </c>
-      <c r="C195" t="s">
-        <v>35</v>
-      </c>
-      <c r="D195">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="196" spans="1:4">
-      <c r="A196" t="s">
-        <v>69</v>
-      </c>
-      <c r="B196" t="s">
-        <v>39</v>
-      </c>
-      <c r="C196" t="s">
-        <v>29</v>
-      </c>
-      <c r="D196">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="197" spans="1:4">
-      <c r="A197" t="s">
-        <v>69</v>
-      </c>
-      <c r="B197" t="s">
-        <v>36</v>
-      </c>
-      <c r="C197" t="s">
-        <v>90</v>
-      </c>
-      <c r="D197">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="198" spans="1:4">
-      <c r="A198" t="s">
-        <v>69</v>
-      </c>
-      <c r="B198" t="s">
-        <v>27</v>
-      </c>
-      <c r="C198" t="s">
-        <v>40</v>
-      </c>
-      <c r="D198">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="199" spans="1:4">
-      <c r="A199" t="s">
-        <v>69</v>
-      </c>
-      <c r="B199" t="s">
-        <v>34</v>
-      </c>
-      <c r="C199" t="s">
-        <v>33</v>
-      </c>
-      <c r="D199">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="200" spans="1:4">
-      <c r="A200" t="s">
-        <v>69</v>
-      </c>
-      <c r="B200" t="s">
-        <v>89</v>
-      </c>
-      <c r="C200" t="s">
-        <v>88</v>
-      </c>
-      <c r="D200">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="201" spans="1:4">
-      <c r="A201" t="s">
-        <v>69</v>
-      </c>
-      <c r="B201" t="s">
-        <v>32</v>
-      </c>
-      <c r="C201" t="s">
-        <v>28</v>
-      </c>
-      <c r="D201">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="202" spans="1:4">
-      <c r="A202" t="s">
-        <v>70</v>
-      </c>
-      <c r="B202" t="s">
-        <v>42</v>
-      </c>
-      <c r="C202" t="s">
-        <v>38</v>
-      </c>
-      <c r="D202">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="203" spans="1:4">
-      <c r="A203" t="s">
-        <v>70</v>
-      </c>
-      <c r="B203" t="s">
-        <v>31</v>
-      </c>
-      <c r="C203" t="s">
-        <v>39</v>
-      </c>
-      <c r="D203">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="204" spans="1:4">
-      <c r="A204" t="s">
-        <v>70</v>
-      </c>
-      <c r="B204" t="s">
-        <v>26</v>
-      </c>
-      <c r="C204" t="s">
-        <v>89</v>
-      </c>
-      <c r="D204">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="205" spans="1:4">
-      <c r="A205" t="s">
-        <v>70</v>
-      </c>
-      <c r="B205" t="s">
-        <v>40</v>
-      </c>
-      <c r="C205" t="s">
-        <v>36</v>
-      </c>
-      <c r="D205">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="206" spans="1:4">
-      <c r="A206" t="s">
-        <v>70</v>
-      </c>
-      <c r="B206" t="s">
-        <v>88</v>
-      </c>
-      <c r="C206" t="s">
-        <v>30</v>
-      </c>
-      <c r="D206">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="207" spans="1:4">
-      <c r="A207" t="s">
-        <v>70</v>
-      </c>
-      <c r="B207" t="s">
-        <v>28</v>
-      </c>
-      <c r="C207" t="s">
-        <v>35</v>
-      </c>
-      <c r="D207">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="208" spans="1:4">
-      <c r="A208" t="s">
-        <v>70</v>
-      </c>
-      <c r="B208" t="s">
-        <v>33</v>
-      </c>
-      <c r="C208" t="s">
-        <v>32</v>
-      </c>
-      <c r="D208">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="209" spans="1:4">
-      <c r="A209" t="s">
-        <v>70</v>
-      </c>
-      <c r="B209" t="s">
-        <v>41</v>
-      </c>
-      <c r="C209" t="s">
-        <v>37</v>
-      </c>
-      <c r="D209">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="210" spans="1:4">
-      <c r="A210" t="s">
-        <v>70</v>
-      </c>
-      <c r="B210" t="s">
-        <v>29</v>
-      </c>
-      <c r="C210" t="s">
-        <v>27</v>
-      </c>
-      <c r="D210">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="211" spans="1:4">
-      <c r="A211" t="s">
-        <v>70</v>
-      </c>
-      <c r="B211" t="s">
-        <v>90</v>
-      </c>
-      <c r="C211" t="s">
-        <v>34</v>
-      </c>
-      <c r="D211">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="212" spans="1:4">
-      <c r="A212" t="s">
-        <v>71</v>
-      </c>
-      <c r="B212" t="s">
-        <v>30</v>
-      </c>
-      <c r="C212" t="s">
-        <v>31</v>
-      </c>
-      <c r="D212">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="213" spans="1:4">
-      <c r="A213" t="s">
-        <v>71</v>
-      </c>
-      <c r="B213" t="s">
-        <v>90</v>
-      </c>
-      <c r="C213" t="s">
-        <v>28</v>
-      </c>
-      <c r="D213">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="214" spans="1:4">
-      <c r="A214" t="s">
-        <v>71</v>
-      </c>
-      <c r="B214" t="s">
-        <v>38</v>
-      </c>
-      <c r="C214" t="s">
-        <v>88</v>
-      </c>
-      <c r="D214">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="215" spans="1:4">
-      <c r="A215" t="s">
-        <v>71</v>
-      </c>
-      <c r="B215" t="s">
-        <v>35</v>
-      </c>
-      <c r="C215" t="s">
-        <v>33</v>
-      </c>
-      <c r="D215">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="216" spans="1:4">
-      <c r="A216" t="s">
-        <v>71</v>
-      </c>
-      <c r="B216" t="s">
-        <v>36</v>
-      </c>
-      <c r="C216" t="s">
-        <v>29</v>
-      </c>
-      <c r="D216">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="217" spans="1:4">
-      <c r="A217" t="s">
-        <v>71</v>
-      </c>
-      <c r="B217" t="s">
-        <v>41</v>
-      </c>
-      <c r="C217" t="s">
-        <v>42</v>
-      </c>
-      <c r="D217">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="218" spans="1:4">
-      <c r="A218" t="s">
-        <v>71</v>
-      </c>
-      <c r="B218" t="s">
-        <v>39</v>
-      </c>
-      <c r="C218" t="s">
-        <v>37</v>
-      </c>
-      <c r="D218">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="219" spans="1:4">
-      <c r="A219" t="s">
-        <v>71</v>
-      </c>
-      <c r="B219" t="s">
-        <v>32</v>
-      </c>
-      <c r="C219" t="s">
-        <v>40</v>
-      </c>
-      <c r="D219">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="220" spans="1:4">
-      <c r="A220" t="s">
-        <v>71</v>
-      </c>
-      <c r="B220" t="s">
-        <v>34</v>
-      </c>
-      <c r="C220" t="s">
-        <v>89</v>
-      </c>
-      <c r="D220">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="221" spans="1:4">
-      <c r="A221" t="s">
-        <v>71</v>
-      </c>
-      <c r="B221" t="s">
-        <v>27</v>
-      </c>
-      <c r="C221" t="s">
-        <v>26</v>
-      </c>
-      <c r="D221">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="222" spans="1:4">
-      <c r="A222" t="s">
-        <v>72</v>
-      </c>
-      <c r="B222" t="s">
-        <v>31</v>
-      </c>
-      <c r="C222" t="s">
-        <v>36</v>
-      </c>
-      <c r="D222">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="223" spans="1:4">
-      <c r="A223" t="s">
-        <v>72</v>
-      </c>
-      <c r="B223" t="s">
-        <v>26</v>
-      </c>
-      <c r="C223" t="s">
-        <v>39</v>
-      </c>
-      <c r="D223">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="224" spans="1:4">
-      <c r="A224" t="s">
-        <v>72</v>
-      </c>
-      <c r="B224" t="s">
-        <v>29</v>
-      </c>
-      <c r="C224" t="s">
-        <v>90</v>
-      </c>
-      <c r="D224">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="225" spans="1:4">
-      <c r="A225" t="s">
-        <v>72</v>
-      </c>
-      <c r="B225" t="s">
-        <v>42</v>
-      </c>
-      <c r="C225" t="s">
-        <v>27</v>
-      </c>
-      <c r="D225">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="226" spans="1:4">
-      <c r="A226" t="s">
-        <v>72</v>
-      </c>
-      <c r="B226" t="s">
-        <v>89</v>
-      </c>
-      <c r="C226" t="s">
-        <v>41</v>
-      </c>
-      <c r="D226">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="227" spans="1:4">
-      <c r="A227" t="s">
-        <v>72</v>
-      </c>
-      <c r="B227" t="s">
-        <v>28</v>
-      </c>
-      <c r="C227" t="s">
-        <v>38</v>
-      </c>
-      <c r="D227">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="228" spans="1:4">
-      <c r="A228" t="s">
-        <v>72</v>
-      </c>
-      <c r="B228" t="s">
-        <v>32</v>
-      </c>
-      <c r="C228" t="s">
-        <v>34</v>
-      </c>
-      <c r="D228">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="229" spans="1:4">
-      <c r="A229" t="s">
-        <v>72</v>
-      </c>
-      <c r="B229" t="s">
-        <v>37</v>
-      </c>
-      <c r="C229" t="s">
-        <v>88</v>
-      </c>
-      <c r="D229">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="230" spans="1:4">
-      <c r="A230" t="s">
-        <v>72</v>
-      </c>
-      <c r="B230" t="s">
-        <v>33</v>
-      </c>
-      <c r="C230" t="s">
-        <v>30</v>
-      </c>
-      <c r="D230">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="231" spans="1:4">
-      <c r="A231" t="s">
-        <v>72</v>
-      </c>
-      <c r="B231" t="s">
-        <v>40</v>
-      </c>
-      <c r="C231" t="s">
-        <v>35</v>
-      </c>
-      <c r="D231">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="232" spans="1:4">
-      <c r="A232" t="s">
-        <v>73</v>
-      </c>
-      <c r="B232" t="s">
-        <v>27</v>
-      </c>
-      <c r="C232" t="s">
-        <v>31</v>
-      </c>
-      <c r="D232">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="233" spans="1:4">
-      <c r="A233" t="s">
-        <v>73</v>
-      </c>
-      <c r="B233" t="s">
-        <v>90</v>
-      </c>
-      <c r="C233" t="s">
-        <v>42</v>
-      </c>
-      <c r="D233">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="234" spans="1:4">
-      <c r="A234" t="s">
-        <v>73</v>
-      </c>
-      <c r="B234" t="s">
-        <v>38</v>
-      </c>
-      <c r="C234" t="s">
-        <v>36</v>
-      </c>
-      <c r="D234">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="235" spans="1:4">
-      <c r="A235" t="s">
-        <v>73</v>
-      </c>
-      <c r="B235" t="s">
-        <v>88</v>
-      </c>
-      <c r="C235" t="s">
-        <v>40</v>
-      </c>
-      <c r="D235">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="236" spans="1:4">
-      <c r="A236" t="s">
-        <v>73</v>
-      </c>
-      <c r="B236" t="s">
-        <v>33</v>
-      </c>
-      <c r="C236" t="s">
-        <v>29</v>
-      </c>
-      <c r="D236">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="237" spans="1:4">
-      <c r="A237" t="s">
-        <v>73</v>
-      </c>
-      <c r="B237" t="s">
-        <v>28</v>
-      </c>
-      <c r="C237" t="s">
-        <v>37</v>
-      </c>
-      <c r="D237">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="238" spans="1:4">
-      <c r="A238" t="s">
-        <v>73</v>
-      </c>
-      <c r="B238" t="s">
-        <v>35</v>
-      </c>
-      <c r="C238" t="s">
-        <v>89</v>
-      </c>
-      <c r="D238">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="239" spans="1:4">
-      <c r="A239" t="s">
-        <v>73</v>
-      </c>
-      <c r="B239" t="s">
-        <v>41</v>
-      </c>
-      <c r="C239" t="s">
-        <v>32</v>
-      </c>
-      <c r="D239">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="240" spans="1:4">
-      <c r="A240" t="s">
-        <v>73</v>
-      </c>
-      <c r="B240" t="s">
-        <v>39</v>
-      </c>
-      <c r="C240" t="s">
-        <v>34</v>
-      </c>
-      <c r="D240">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="241" spans="1:4">
-      <c r="A241" t="s">
-        <v>73</v>
-      </c>
-      <c r="B241" t="s">
-        <v>26</v>
-      </c>
-      <c r="C241" t="s">
-        <v>30</v>
-      </c>
-      <c r="D241">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="242" spans="1:4">
-      <c r="A242" t="s">
-        <v>74</v>
-      </c>
-      <c r="B242" t="s">
-        <v>29</v>
-      </c>
-      <c r="C242" t="s">
-        <v>38</v>
-      </c>
-      <c r="D242">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="243" spans="1:4">
-      <c r="A243" t="s">
-        <v>74</v>
-      </c>
-      <c r="B243" t="s">
-        <v>32</v>
-      </c>
-      <c r="C243" t="s">
-        <v>90</v>
-      </c>
-      <c r="D243">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="244" spans="1:4">
-      <c r="A244" t="s">
-        <v>74</v>
-      </c>
-      <c r="B244" t="s">
-        <v>35</v>
-      </c>
-      <c r="C244" t="s">
-        <v>37</v>
-      </c>
-      <c r="D244">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="245" spans="1:4">
-      <c r="A245" t="s">
-        <v>74</v>
-      </c>
-      <c r="B245" t="s">
-        <v>31</v>
-      </c>
-      <c r="C245" t="s">
-        <v>33</v>
-      </c>
-      <c r="D245">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="246" spans="1:4">
-      <c r="A246" t="s">
-        <v>74</v>
-      </c>
-      <c r="B246" t="s">
-        <v>40</v>
-      </c>
-      <c r="C246" t="s">
-        <v>26</v>
-      </c>
-      <c r="D246">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="247" spans="1:4">
-      <c r="A247" t="s">
-        <v>74</v>
-      </c>
-      <c r="B247" t="s">
-        <v>36</v>
-      </c>
-      <c r="C247" t="s">
-        <v>28</v>
-      </c>
-      <c r="D247">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="248" spans="1:4">
-      <c r="A248" t="s">
-        <v>74</v>
-      </c>
-      <c r="B248" t="s">
-        <v>30</v>
-      </c>
-      <c r="C248" t="s">
-        <v>41</v>
-      </c>
-      <c r="D248">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="249" spans="1:4">
-      <c r="A249" t="s">
-        <v>74</v>
-      </c>
-      <c r="B249" t="s">
-        <v>89</v>
-      </c>
-      <c r="C249" t="s">
-        <v>39</v>
-      </c>
-      <c r="D249">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="250" spans="1:4">
-      <c r="A250" t="s">
-        <v>74</v>
-      </c>
-      <c r="B250" t="s">
-        <v>42</v>
-      </c>
-      <c r="C250" t="s">
-        <v>88</v>
-      </c>
-      <c r="D250">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="251" spans="1:4">
-      <c r="A251" t="s">
-        <v>74</v>
-      </c>
-      <c r="B251" t="s">
-        <v>34</v>
-      </c>
-      <c r="C251" t="s">
-        <v>27</v>
-      </c>
-      <c r="D251">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="252" spans="1:4">
-      <c r="A252" t="s">
-        <v>75</v>
-      </c>
-      <c r="B252" t="s">
-        <v>26</v>
-      </c>
-      <c r="C252" t="s">
-        <v>32</v>
-      </c>
-      <c r="D252">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="253" spans="1:4">
-      <c r="A253" t="s">
-        <v>75</v>
-      </c>
-      <c r="B253" t="s">
-        <v>39</v>
-      </c>
-      <c r="C253" t="s">
-        <v>35</v>
-      </c>
-      <c r="D253">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="254" spans="1:4">
-      <c r="A254" t="s">
-        <v>75</v>
-      </c>
-      <c r="B254" t="s">
-        <v>37</v>
-      </c>
-      <c r="C254" t="s">
-        <v>36</v>
-      </c>
-      <c r="D254">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="255" spans="1:4">
-      <c r="A255" t="s">
-        <v>75</v>
-      </c>
-      <c r="B255" t="s">
-        <v>41</v>
-      </c>
-      <c r="C255" t="s">
-        <v>34</v>
-      </c>
-      <c r="D255">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="256" spans="1:4">
-      <c r="A256" t="s">
-        <v>75</v>
-      </c>
-      <c r="B256" t="s">
-        <v>28</v>
-      </c>
-      <c r="C256" t="s">
-        <v>89</v>
-      </c>
-      <c r="D256">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="257" spans="1:4">
-      <c r="A257" t="s">
-        <v>75</v>
-      </c>
-      <c r="B257" t="s">
-        <v>29</v>
-      </c>
-      <c r="C257" t="s">
-        <v>30</v>
-      </c>
-      <c r="D257">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="258" spans="1:4">
-      <c r="A258" t="s">
-        <v>75</v>
-      </c>
-      <c r="B258" t="s">
-        <v>38</v>
-      </c>
-      <c r="C258" t="s">
-        <v>40</v>
-      </c>
-      <c r="D258">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="259" spans="1:4">
-      <c r="A259" t="s">
-        <v>75</v>
-      </c>
-      <c r="B259" t="s">
-        <v>33</v>
-      </c>
-      <c r="C259" t="s">
-        <v>42</v>
-      </c>
-      <c r="D259">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="260" spans="1:4">
-      <c r="A260" t="s">
-        <v>75</v>
-      </c>
-      <c r="B260" t="s">
-        <v>90</v>
-      </c>
-      <c r="C260" t="s">
-        <v>31</v>
-      </c>
-      <c r="D260">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="261" spans="1:4">
-      <c r="A261" t="s">
-        <v>75</v>
-      </c>
-      <c r="B261" t="s">
-        <v>88</v>
-      </c>
-      <c r="C261" t="s">
-        <v>27</v>
-      </c>
-      <c r="D261">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="262" spans="1:4">
-      <c r="A262" t="s">
-        <v>76</v>
-      </c>
-      <c r="B262" t="s">
-        <v>35</v>
-      </c>
-      <c r="C262" t="s">
-        <v>26</v>
-      </c>
-      <c r="D262">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="263" spans="1:4">
-      <c r="A263" t="s">
-        <v>76</v>
-      </c>
-      <c r="B263" t="s">
-        <v>32</v>
-      </c>
-      <c r="C263" t="s">
-        <v>38</v>
-      </c>
-      <c r="D263">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="264" spans="1:4">
-      <c r="A264" t="s">
-        <v>76</v>
-      </c>
-      <c r="B264" t="s">
-        <v>27</v>
-      </c>
-      <c r="C264" t="s">
-        <v>37</v>
-      </c>
-      <c r="D264">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="265" spans="1:4">
-      <c r="A265" t="s">
-        <v>76</v>
-      </c>
-      <c r="B265" t="s">
-        <v>42</v>
-      </c>
-      <c r="C265" t="s">
-        <v>29</v>
-      </c>
-      <c r="D265">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="266" spans="1:4">
-      <c r="A266" t="s">
-        <v>76</v>
-      </c>
-      <c r="B266" t="s">
-        <v>34</v>
-      </c>
-      <c r="C266" t="s">
-        <v>88</v>
-      </c>
-      <c r="D266">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="267" spans="1:4">
-      <c r="A267" t="s">
-        <v>76</v>
-      </c>
-      <c r="B267" t="s">
-        <v>36</v>
-      </c>
-      <c r="C267" t="s">
-        <v>33</v>
-      </c>
-      <c r="D267">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="268" spans="1:4">
-      <c r="A268" t="s">
-        <v>76</v>
-      </c>
-      <c r="B268" t="s">
-        <v>90</v>
-      </c>
-      <c r="C268" t="s">
-        <v>41</v>
-      </c>
-      <c r="D268">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="269" spans="1:4">
-      <c r="A269" t="s">
-        <v>76</v>
-      </c>
-      <c r="B269" t="s">
-        <v>40</v>
-      </c>
-      <c r="C269" t="s">
-        <v>89</v>
-      </c>
-      <c r="D269">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="270" spans="1:4">
-      <c r="A270" t="s">
-        <v>76</v>
-      </c>
-      <c r="B270" t="s">
-        <v>30</v>
-      </c>
-      <c r="C270" t="s">
-        <v>39</v>
-      </c>
-      <c r="D270">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="271" spans="1:4">
-      <c r="A271" t="s">
-        <v>76</v>
-      </c>
-      <c r="B271" t="s">
-        <v>31</v>
-      </c>
-      <c r="C271" t="s">
-        <v>28</v>
-      </c>
-      <c r="D271">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="272" spans="1:4">
-      <c r="A272" t="s">
-        <v>77</v>
-      </c>
-      <c r="B272" t="s">
-        <v>33</v>
-      </c>
-      <c r="C272" t="s">
-        <v>27</v>
-      </c>
-      <c r="D272">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="273" spans="1:4">
-      <c r="A273" t="s">
-        <v>77</v>
-      </c>
-      <c r="B273" t="s">
-        <v>39</v>
-      </c>
-      <c r="C273" t="s">
-        <v>40</v>
-      </c>
-      <c r="D273">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="274" spans="1:4">
-      <c r="A274" t="s">
-        <v>77</v>
-      </c>
-      <c r="B274" t="s">
-        <v>30</v>
-      </c>
-      <c r="C274" t="s">
-        <v>36</v>
-      </c>
-      <c r="D274">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="275" spans="1:4">
-      <c r="A275" t="s">
-        <v>77</v>
-      </c>
-      <c r="B275" t="s">
-        <v>41</v>
-      </c>
-      <c r="C275" t="s">
-        <v>28</v>
-      </c>
-      <c r="D275">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="276" spans="1:4">
-      <c r="A276" t="s">
-        <v>77</v>
-      </c>
-      <c r="B276" t="s">
-        <v>37</v>
-      </c>
-      <c r="C276" t="s">
-        <v>42</v>
-      </c>
-      <c r="D276">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="277" spans="1:4">
-      <c r="A277" t="s">
-        <v>77</v>
-      </c>
-      <c r="B277" t="s">
-        <v>38</v>
-      </c>
-      <c r="C277" t="s">
-        <v>26</v>
-      </c>
-      <c r="D277">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="278" spans="1:4">
-      <c r="A278" t="s">
-        <v>77</v>
-      </c>
-      <c r="B278" t="s">
-        <v>88</v>
-      </c>
-      <c r="C278" t="s">
-        <v>90</v>
-      </c>
-      <c r="D278">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="279" spans="1:4">
-      <c r="A279" t="s">
-        <v>77</v>
-      </c>
-      <c r="B279" t="s">
-        <v>29</v>
-      </c>
-      <c r="C279" t="s">
-        <v>35</v>
-      </c>
-      <c r="D279">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="280" spans="1:4">
-      <c r="A280" t="s">
-        <v>77</v>
-      </c>
-      <c r="B280" t="s">
-        <v>34</v>
-      </c>
-      <c r="C280" t="s">
-        <v>31</v>
-      </c>
-      <c r="D280">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="281" spans="1:4">
-      <c r="A281" t="s">
-        <v>77</v>
-      </c>
-      <c r="B281" t="s">
-        <v>89</v>
-      </c>
-      <c r="C281" t="s">
-        <v>32</v>
-      </c>
-      <c r="D281">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="282" spans="1:4">
-      <c r="A282" t="s">
-        <v>78</v>
-      </c>
-      <c r="B282" t="s">
-        <v>27</v>
-      </c>
-      <c r="C282" t="s">
-        <v>89</v>
-      </c>
-      <c r="D282">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="283" spans="1:4">
-      <c r="A283" t="s">
-        <v>78</v>
-      </c>
-      <c r="B283" t="s">
-        <v>35</v>
-      </c>
-      <c r="C283" t="s">
-        <v>38</v>
-      </c>
-      <c r="D283">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="284" spans="1:4">
-      <c r="A284" t="s">
-        <v>78</v>
-      </c>
-      <c r="B284" t="s">
-        <v>31</v>
-      </c>
-      <c r="C284" t="s">
-        <v>29</v>
-      </c>
-      <c r="D284">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="285" spans="1:4">
-      <c r="A285" t="s">
-        <v>78</v>
-      </c>
-      <c r="B285" t="s">
-        <v>40</v>
-      </c>
-      <c r="C285" t="s">
-        <v>41</v>
-      </c>
-      <c r="D285">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="286" spans="1:4">
-      <c r="A286" t="s">
-        <v>78</v>
-      </c>
-      <c r="B286" t="s">
-        <v>37</v>
-      </c>
-      <c r="C286" t="s">
-        <v>34</v>
-      </c>
-      <c r="D286">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="287" spans="1:4">
-      <c r="A287" t="s">
-        <v>78</v>
-      </c>
-      <c r="B287" t="s">
-        <v>36</v>
-      </c>
-      <c r="C287" t="s">
-        <v>39</v>
-      </c>
-      <c r="D287">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="288" spans="1:4">
-      <c r="A288" t="s">
-        <v>78</v>
-      </c>
-      <c r="B288" t="s">
-        <v>90</v>
-      </c>
-      <c r="C288" t="s">
-        <v>33</v>
-      </c>
-      <c r="D288">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="289" spans="1:4">
-      <c r="A289" t="s">
-        <v>78</v>
-      </c>
-      <c r="B289" t="s">
-        <v>26</v>
-      </c>
-      <c r="C289" t="s">
-        <v>88</v>
-      </c>
-      <c r="D289">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="290" spans="1:4">
-      <c r="A290" t="s">
-        <v>78</v>
-      </c>
-      <c r="B290" t="s">
-        <v>28</v>
-      </c>
-      <c r="C290" t="s">
-        <v>42</v>
-      </c>
-      <c r="D290">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="291" spans="1:4">
-      <c r="A291" t="s">
-        <v>78</v>
-      </c>
-      <c r="B291" t="s">
-        <v>32</v>
-      </c>
-      <c r="C291" t="s">
-        <v>30</v>
-      </c>
-      <c r="D291">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="292" spans="1:4">
-      <c r="A292" t="s">
-        <v>79</v>
-      </c>
-      <c r="B292" t="s">
-        <v>42</v>
-      </c>
-      <c r="C292" t="s">
-        <v>34</v>
-      </c>
-      <c r="D292">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="293" spans="1:4">
-      <c r="A293" t="s">
-        <v>79</v>
-      </c>
-      <c r="B293" t="s">
-        <v>39</v>
-      </c>
-      <c r="C293" t="s">
-        <v>27</v>
-      </c>
-      <c r="D293">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="294" spans="1:4">
-      <c r="A294" t="s">
-        <v>79</v>
-      </c>
-      <c r="B294" t="s">
-        <v>29</v>
-      </c>
-      <c r="C294" t="s">
-        <v>40</v>
-      </c>
-      <c r="D294">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="295" spans="1:4">
-      <c r="A295" t="s">
-        <v>79</v>
-      </c>
-      <c r="B295" t="s">
-        <v>36</v>
-      </c>
-      <c r="C295" t="s">
-        <v>32</v>
-      </c>
-      <c r="D295">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="296" spans="1:4">
-      <c r="A296" t="s">
-        <v>79</v>
-      </c>
-      <c r="B296" t="s">
-        <v>28</v>
-      </c>
-      <c r="C296" t="s">
-        <v>33</v>
-      </c>
-      <c r="D296">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="297" spans="1:4">
-      <c r="A297" t="s">
-        <v>79</v>
-      </c>
-      <c r="B297" t="s">
-        <v>30</v>
-      </c>
-      <c r="C297" t="s">
-        <v>90</v>
-      </c>
-      <c r="D297">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="298" spans="1:4">
-      <c r="A298" t="s">
-        <v>79</v>
-      </c>
-      <c r="B298" t="s">
-        <v>41</v>
-      </c>
-      <c r="C298" t="s">
-        <v>26</v>
-      </c>
-      <c r="D298">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="299" spans="1:4">
-      <c r="A299" t="s">
-        <v>79</v>
-      </c>
-      <c r="B299" t="s">
-        <v>38</v>
-      </c>
-      <c r="C299" t="s">
-        <v>31</v>
-      </c>
-      <c r="D299">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="300" spans="1:4">
-      <c r="A300" t="s">
-        <v>79</v>
-      </c>
-      <c r="B300" t="s">
-        <v>89</v>
-      </c>
-      <c r="C300" t="s">
-        <v>37</v>
-      </c>
-      <c r="D300">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="301" spans="1:4">
-      <c r="A301" t="s">
-        <v>79</v>
-      </c>
-      <c r="B301" t="s">
-        <v>88</v>
-      </c>
-      <c r="C301" t="s">
-        <v>35</v>
-      </c>
-      <c r="D301">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="302" spans="1:4">
-      <c r="A302" t="s">
-        <v>80</v>
-      </c>
-      <c r="B302" t="s">
-        <v>31</v>
-      </c>
-      <c r="C302" t="s">
-        <v>42</v>
-      </c>
-      <c r="D302">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="303" spans="1:4">
-      <c r="A303" t="s">
-        <v>80</v>
-      </c>
-      <c r="B303" t="s">
-        <v>27</v>
-      </c>
-      <c r="C303" t="s">
-        <v>36</v>
-      </c>
-      <c r="D303">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="304" spans="1:4">
-      <c r="A304" t="s">
-        <v>80</v>
-      </c>
-      <c r="B304" t="s">
-        <v>40</v>
-      </c>
-      <c r="C304" t="s">
-        <v>30</v>
-      </c>
-      <c r="D304">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="305" spans="1:4">
-      <c r="A305" t="s">
-        <v>80</v>
-      </c>
-      <c r="B305" t="s">
-        <v>34</v>
-      </c>
-      <c r="C305" t="s">
-        <v>38</v>
-      </c>
-      <c r="D305">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="306" spans="1:4">
-      <c r="A306" t="s">
-        <v>80</v>
-      </c>
-      <c r="B306" t="s">
-        <v>39</v>
-      </c>
-      <c r="C306" t="s">
-        <v>32</v>
-      </c>
-      <c r="D306">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="307" spans="1:4">
-      <c r="A307" t="s">
-        <v>80</v>
-      </c>
-      <c r="B307" t="s">
-        <v>37</v>
-      </c>
-      <c r="C307" t="s">
-        <v>29</v>
-      </c>
-      <c r="D307">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="308" spans="1:4">
-      <c r="A308" t="s">
-        <v>80</v>
-      </c>
-      <c r="B308" t="s">
-        <v>33</v>
-      </c>
-      <c r="C308" t="s">
-        <v>89</v>
-      </c>
-      <c r="D308">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="309" spans="1:4">
-      <c r="A309" t="s">
-        <v>80</v>
-      </c>
-      <c r="B309" t="s">
-        <v>88</v>
-      </c>
-      <c r="C309" t="s">
-        <v>41</v>
-      </c>
-      <c r="D309">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="310" spans="1:4">
-      <c r="A310" t="s">
-        <v>80</v>
-      </c>
-      <c r="B310" t="s">
-        <v>26</v>
-      </c>
-      <c r="C310" t="s">
-        <v>28</v>
-      </c>
-      <c r="D310">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="311" spans="1:4">
-      <c r="A311" t="s">
-        <v>80</v>
-      </c>
-      <c r="B311" t="s">
-        <v>35</v>
-      </c>
-      <c r="C311" t="s">
-        <v>90</v>
-      </c>
-      <c r="D311">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="312" spans="1:4">
-      <c r="A312" t="s">
-        <v>81</v>
-      </c>
-      <c r="B312" t="s">
-        <v>90</v>
-      </c>
-      <c r="C312" t="s">
-        <v>26</v>
-      </c>
-      <c r="D312">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="313" spans="1:4">
-      <c r="A313" t="s">
-        <v>81</v>
-      </c>
-      <c r="B313" t="s">
-        <v>40</v>
-      </c>
-      <c r="C313" t="s">
-        <v>37</v>
-      </c>
-      <c r="D313">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="314" spans="1:4">
-      <c r="A314" t="s">
-        <v>81</v>
-      </c>
-      <c r="B314" t="s">
-        <v>28</v>
-      </c>
-      <c r="C314" t="s">
-        <v>34</v>
-      </c>
-      <c r="D314">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="315" spans="1:4">
-      <c r="A315" t="s">
-        <v>81</v>
-      </c>
-      <c r="B315" t="s">
-        <v>29</v>
-      </c>
-      <c r="C315" t="s">
-        <v>88</v>
-      </c>
-      <c r="D315">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="316" spans="1:4">
-      <c r="A316" t="s">
-        <v>81</v>
-      </c>
-      <c r="B316" t="s">
-        <v>36</v>
-      </c>
-      <c r="C316" t="s">
-        <v>42</v>
-      </c>
-      <c r="D316">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="317" spans="1:4">
-      <c r="A317" t="s">
-        <v>81</v>
-      </c>
-      <c r="B317" t="s">
-        <v>33</v>
-      </c>
-      <c r="C317" t="s">
-        <v>39</v>
-      </c>
-      <c r="D317">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="318" spans="1:4">
-      <c r="A318" t="s">
-        <v>81</v>
-      </c>
-      <c r="B318" t="s">
-        <v>32</v>
-      </c>
-      <c r="C318" t="s">
-        <v>35</v>
-      </c>
-      <c r="D318">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="319" spans="1:4">
-      <c r="A319" t="s">
-        <v>81</v>
-      </c>
-      <c r="B319" t="s">
-        <v>89</v>
-      </c>
-      <c r="C319" t="s">
-        <v>31</v>
-      </c>
-      <c r="D319">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="320" spans="1:4">
-      <c r="A320" t="s">
-        <v>81</v>
-      </c>
-      <c r="B320" t="s">
-        <v>30</v>
-      </c>
-      <c r="C320" t="s">
-        <v>27</v>
-      </c>
-      <c r="D320">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="321" spans="1:4">
-      <c r="A321" t="s">
-        <v>81</v>
-      </c>
-      <c r="B321" t="s">
-        <v>38</v>
-      </c>
-      <c r="C321" t="s">
-        <v>41</v>
-      </c>
-      <c r="D321">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="322" spans="1:4">
-      <c r="A322" t="s">
-        <v>82</v>
-      </c>
-      <c r="B322" t="s">
-        <v>88</v>
-      </c>
-      <c r="C322" t="s">
-        <v>28</v>
-      </c>
-      <c r="D322">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="323" spans="1:4">
-      <c r="A323" t="s">
-        <v>82</v>
-      </c>
-      <c r="B323" t="s">
-        <v>39</v>
-      </c>
-      <c r="C323" t="s">
-        <v>90</v>
-      </c>
-      <c r="D323">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="324" spans="1:4">
-      <c r="A324" t="s">
-        <v>82</v>
-      </c>
-      <c r="B324" t="s">
-        <v>27</v>
-      </c>
-      <c r="C324" t="s">
-        <v>35</v>
-      </c>
-      <c r="D324">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="325" spans="1:4">
-      <c r="A325" t="s">
-        <v>82</v>
-      </c>
-      <c r="B325" t="s">
-        <v>37</v>
-      </c>
-      <c r="C325" t="s">
-        <v>32</v>
-      </c>
-      <c r="D325">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="326" spans="1:4">
-      <c r="A326" t="s">
-        <v>82</v>
-      </c>
-      <c r="B326" t="s">
-        <v>34</v>
-      </c>
-      <c r="C326" t="s">
-        <v>29</v>
-      </c>
-      <c r="D326">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="327" spans="1:4">
-      <c r="A327" t="s">
-        <v>82</v>
-      </c>
-      <c r="B327" t="s">
-        <v>31</v>
-      </c>
-      <c r="C327" t="s">
-        <v>40</v>
-      </c>
-      <c r="D327">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="328" spans="1:4">
-      <c r="A328" t="s">
-        <v>82</v>
-      </c>
-      <c r="B328" t="s">
-        <v>41</v>
-      </c>
-      <c r="C328" t="s">
-        <v>36</v>
-      </c>
-      <c r="D328">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="329" spans="1:4">
-      <c r="A329" t="s">
-        <v>82</v>
-      </c>
-      <c r="B329" t="s">
-        <v>42</v>
-      </c>
-      <c r="C329" t="s">
-        <v>30</v>
-      </c>
-      <c r="D329">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="330" spans="1:4">
-      <c r="A330" t="s">
-        <v>82</v>
-      </c>
-      <c r="B330" t="s">
-        <v>89</v>
-      </c>
-      <c r="C330" t="s">
-        <v>38</v>
-      </c>
-      <c r="D330">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="331" spans="1:4">
-      <c r="A331" t="s">
-        <v>82</v>
-      </c>
-      <c r="B331" t="s">
-        <v>26</v>
-      </c>
-      <c r="C331" t="s">
-        <v>33</v>
-      </c>
-      <c r="D331">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="332" spans="1:4">
-      <c r="A332" t="s">
-        <v>83</v>
-      </c>
-      <c r="B332" t="s">
-        <v>32</v>
-      </c>
-      <c r="C332" t="s">
-        <v>31</v>
-      </c>
-      <c r="D332">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="333" spans="1:4">
-      <c r="A333" t="s">
-        <v>83</v>
-      </c>
-      <c r="B333" t="s">
-        <v>38</v>
-      </c>
-      <c r="C333" t="s">
-        <v>37</v>
-      </c>
-      <c r="D333">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="334" spans="1:4">
-      <c r="A334" t="s">
-        <v>83</v>
-      </c>
-      <c r="B334" t="s">
-        <v>30</v>
-      </c>
-      <c r="C334" t="s">
-        <v>34</v>
-      </c>
-      <c r="D334">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="335" spans="1:4">
-      <c r="A335" t="s">
-        <v>83</v>
-      </c>
-      <c r="B335" t="s">
-        <v>35</v>
-      </c>
-      <c r="C335" t="s">
-        <v>41</v>
-      </c>
-      <c r="D335">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="336" spans="1:4">
-      <c r="A336" t="s">
-        <v>83</v>
-      </c>
-      <c r="B336" t="s">
-        <v>36</v>
-      </c>
-      <c r="C336" t="s">
-        <v>88</v>
-      </c>
-      <c r="D336">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="337" spans="1:4">
-      <c r="A337" t="s">
-        <v>83</v>
-      </c>
-      <c r="B337" t="s">
-        <v>33</v>
-      </c>
-      <c r="C337" t="s">
-        <v>40</v>
-      </c>
-      <c r="D337">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="338" spans="1:4">
-      <c r="A338" t="s">
-        <v>83</v>
-      </c>
-      <c r="B338" t="s">
-        <v>29</v>
-      </c>
-      <c r="C338" t="s">
-        <v>26</v>
-      </c>
-      <c r="D338">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="339" spans="1:4">
-      <c r="A339" t="s">
-        <v>83</v>
-      </c>
-      <c r="B339" t="s">
-        <v>90</v>
-      </c>
-      <c r="C339" t="s">
-        <v>89</v>
-      </c>
-      <c r="D339">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="340" spans="1:4">
-      <c r="A340" t="s">
-        <v>83</v>
-      </c>
-      <c r="B340" t="s">
-        <v>42</v>
-      </c>
-      <c r="C340" t="s">
-        <v>39</v>
-      </c>
-      <c r="D340">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="341" spans="1:4">
-      <c r="A341" t="s">
-        <v>83</v>
-      </c>
-      <c r="B341" t="s">
-        <v>28</v>
-      </c>
-      <c r="C341" t="s">
-        <v>27</v>
-      </c>
-      <c r="D341">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="342" spans="1:4">
-      <c r="A342" t="s">
-        <v>84</v>
-      </c>
-      <c r="B342" t="s">
-        <v>37</v>
-      </c>
-      <c r="C342" t="s">
-        <v>30</v>
-      </c>
-      <c r="D342">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="343" spans="1:4">
-      <c r="A343" t="s">
-        <v>84</v>
-      </c>
-      <c r="B343" t="s">
-        <v>41</v>
-      </c>
-      <c r="C343" t="s">
-        <v>39</v>
-      </c>
-      <c r="D343">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="344" spans="1:4">
-      <c r="A344" t="s">
-        <v>84</v>
-      </c>
-      <c r="B344" t="s">
-        <v>34</v>
-      </c>
-      <c r="C344" t="s">
-        <v>36</v>
-      </c>
-      <c r="D344">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="345" spans="1:4">
-      <c r="A345" t="s">
-        <v>84</v>
-      </c>
-      <c r="B345" t="s">
-        <v>27</v>
-      </c>
-      <c r="C345" t="s">
-        <v>90</v>
-      </c>
-      <c r="D345">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="346" spans="1:4">
-      <c r="A346" t="s">
-        <v>84</v>
-      </c>
-      <c r="B346" t="s">
-        <v>26</v>
-      </c>
-      <c r="C346" t="s">
-        <v>42</v>
-      </c>
-      <c r="D346">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="347" spans="1:4">
-      <c r="A347" t="s">
-        <v>84</v>
-      </c>
-      <c r="B347" t="s">
-        <v>89</v>
-      </c>
-      <c r="C347" t="s">
-        <v>29</v>
-      </c>
-      <c r="D347">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="348" spans="1:4">
-      <c r="A348" t="s">
-        <v>84</v>
-      </c>
-      <c r="B348" t="s">
-        <v>35</v>
-      </c>
-      <c r="C348" t="s">
-        <v>31</v>
-      </c>
-      <c r="D348">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="349" spans="1:4">
-      <c r="A349" t="s">
-        <v>84</v>
-      </c>
-      <c r="B349" t="s">
-        <v>38</v>
-      </c>
-      <c r="C349" t="s">
-        <v>33</v>
-      </c>
-      <c r="D349">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="350" spans="1:4">
-      <c r="A350" t="s">
-        <v>84</v>
-      </c>
-      <c r="B350" t="s">
-        <v>88</v>
-      </c>
-      <c r="C350" t="s">
-        <v>32</v>
-      </c>
-      <c r="D350">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="351" spans="1:4">
-      <c r="A351" t="s">
-        <v>84</v>
-      </c>
-      <c r="B351" t="s">
-        <v>40</v>
-      </c>
-      <c r="C351" t="s">
-        <v>28</v>
-      </c>
-      <c r="D351">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="352" spans="1:4">
-      <c r="A352" t="s">
-        <v>85</v>
-      </c>
-      <c r="B352" t="s">
-        <v>27</v>
-      </c>
-      <c r="C352" t="s">
-        <v>41</v>
-      </c>
-      <c r="D352">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="353" spans="1:4">
-      <c r="A353" t="s">
-        <v>85</v>
-      </c>
-      <c r="B353" t="s">
-        <v>42</v>
-      </c>
-      <c r="C353" t="s">
-        <v>40</v>
-      </c>
-      <c r="D353">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="354" spans="1:4">
-      <c r="A354" t="s">
-        <v>85</v>
-      </c>
-      <c r="B354" t="s">
-        <v>34</v>
-      </c>
-      <c r="C354" t="s">
-        <v>35</v>
-      </c>
-      <c r="D354">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="355" spans="1:4">
-      <c r="A355" t="s">
-        <v>85</v>
-      </c>
-      <c r="B355" t="s">
-        <v>33</v>
-      </c>
-      <c r="C355" t="s">
-        <v>88</v>
-      </c>
-      <c r="D355">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="356" spans="1:4">
-      <c r="A356" t="s">
-        <v>85</v>
-      </c>
-      <c r="B356" t="s">
-        <v>29</v>
-      </c>
-      <c r="C356" t="s">
-        <v>32</v>
-      </c>
-      <c r="D356">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="357" spans="1:4">
-      <c r="A357" t="s">
-        <v>85</v>
-      </c>
-      <c r="B357" t="s">
-        <v>31</v>
-      </c>
-      <c r="C357" t="s">
-        <v>26</v>
-      </c>
-      <c r="D357">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="358" spans="1:4">
-      <c r="A358" t="s">
-        <v>85</v>
-      </c>
-      <c r="B358" t="s">
-        <v>36</v>
-      </c>
-      <c r="C358" t="s">
-        <v>89</v>
-      </c>
-      <c r="D358">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="359" spans="1:4">
-      <c r="A359" t="s">
-        <v>85</v>
-      </c>
-      <c r="B359" t="s">
-        <v>90</v>
-      </c>
-      <c r="C359" t="s">
-        <v>37</v>
-      </c>
-      <c r="D359">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="360" spans="1:4">
-      <c r="A360" t="s">
-        <v>85</v>
-      </c>
-      <c r="B360" t="s">
-        <v>30</v>
-      </c>
-      <c r="C360" t="s">
-        <v>28</v>
-      </c>
-      <c r="D360">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="361" spans="1:4">
-      <c r="A361" t="s">
-        <v>85</v>
-      </c>
-      <c r="B361" t="s">
-        <v>39</v>
-      </c>
-      <c r="C361" t="s">
-        <v>38</v>
-      </c>
-      <c r="D361">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="362" spans="1:4">
-      <c r="A362" t="s">
-        <v>86</v>
-      </c>
-      <c r="B362" t="s">
-        <v>28</v>
-      </c>
-      <c r="C362" t="s">
-        <v>29</v>
-      </c>
-      <c r="D362">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="363" spans="1:4">
-      <c r="A363" t="s">
-        <v>86</v>
-      </c>
-      <c r="B363" t="s">
-        <v>37</v>
-      </c>
-      <c r="C363" t="s">
-        <v>31</v>
-      </c>
-      <c r="D363">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="364" spans="1:4">
-      <c r="A364" t="s">
-        <v>86</v>
-      </c>
-      <c r="B364" t="s">
-        <v>38</v>
-      </c>
-      <c r="C364" t="s">
-        <v>27</v>
-      </c>
-      <c r="D364">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="365" spans="1:4">
-      <c r="A365" t="s">
-        <v>86</v>
-      </c>
-      <c r="B365" t="s">
-        <v>32</v>
-      </c>
-      <c r="C365" t="s">
-        <v>42</v>
-      </c>
-      <c r="D365">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="366" spans="1:4">
-      <c r="A366" t="s">
-        <v>86</v>
-      </c>
-      <c r="B366" t="s">
-        <v>26</v>
-      </c>
-      <c r="C366" t="s">
-        <v>34</v>
-      </c>
-      <c r="D366">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="367" spans="1:4">
-      <c r="A367" t="s">
-        <v>86</v>
-      </c>
-      <c r="B367" t="s">
-        <v>35</v>
-      </c>
-      <c r="C367" t="s">
-        <v>36</v>
-      </c>
-      <c r="D367">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="368" spans="1:4">
-      <c r="A368" t="s">
-        <v>86</v>
-      </c>
-      <c r="B368" t="s">
-        <v>88</v>
-      </c>
-      <c r="C368" t="s">
-        <v>39</v>
-      </c>
-      <c r="D368">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="369" spans="1:4">
-      <c r="A369" t="s">
-        <v>86</v>
-      </c>
-      <c r="B369" t="s">
-        <v>40</v>
-      </c>
-      <c r="C369" t="s">
-        <v>90</v>
-      </c>
-      <c r="D369">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="370" spans="1:4">
-      <c r="A370" t="s">
-        <v>86</v>
-      </c>
-      <c r="B370" t="s">
-        <v>89</v>
-      </c>
-      <c r="C370" t="s">
-        <v>30</v>
-      </c>
-      <c r="D370">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="371" spans="1:4">
-      <c r="A371" t="s">
-        <v>86</v>
-      </c>
-      <c r="B371" t="s">
-        <v>41</v>
-      </c>
-      <c r="C371" t="s">
-        <v>33</v>
-      </c>
-      <c r="D371">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="372" spans="1:4">
-      <c r="A372" t="s">
-        <v>87</v>
-      </c>
-      <c r="B372" t="s">
-        <v>30</v>
-      </c>
-      <c r="C372" t="s">
-        <v>35</v>
-      </c>
-      <c r="D372">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="373" spans="1:4">
-      <c r="A373" t="s">
-        <v>87</v>
-      </c>
-      <c r="B373" t="s">
-        <v>31</v>
-      </c>
-      <c r="C373" t="s">
-        <v>88</v>
-      </c>
-      <c r="D373">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="374" spans="1:4">
-      <c r="A374" t="s">
-        <v>87</v>
-      </c>
-      <c r="B374" t="s">
-        <v>90</v>
-      </c>
-      <c r="C374" t="s">
-        <v>38</v>
-      </c>
-      <c r="D374">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="375" spans="1:4">
-      <c r="A375" t="s">
-        <v>87</v>
-      </c>
-      <c r="B375" t="s">
-        <v>36</v>
-      </c>
-      <c r="C375" t="s">
-        <v>26</v>
-      </c>
-      <c r="D375">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="376" spans="1:4">
-      <c r="A376" t="s">
-        <v>87</v>
-      </c>
-      <c r="B376" t="s">
-        <v>39</v>
-      </c>
-      <c r="C376" t="s">
-        <v>28</v>
-      </c>
-      <c r="D376">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="377" spans="1:4">
-      <c r="A377" t="s">
-        <v>87</v>
-      </c>
-      <c r="B377" t="s">
-        <v>34</v>
-      </c>
-      <c r="C377" t="s">
-        <v>40</v>
-      </c>
-      <c r="D377">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="378" spans="1:4">
-      <c r="A378" t="s">
-        <v>87</v>
-      </c>
-      <c r="B378" t="s">
-        <v>29</v>
-      </c>
-      <c r="C378" t="s">
-        <v>41</v>
-      </c>
-      <c r="D378">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="379" spans="1:4">
-      <c r="A379" t="s">
-        <v>87</v>
-      </c>
-      <c r="B379" t="s">
-        <v>27</v>
-      </c>
-      <c r="C379" t="s">
-        <v>32</v>
-      </c>
-      <c r="D379">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="380" spans="1:4">
-      <c r="A380" t="s">
-        <v>87</v>
-      </c>
-      <c r="B380" t="s">
-        <v>42</v>
-      </c>
-      <c r="C380" t="s">
-        <v>89</v>
-      </c>
-      <c r="D380">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="381" spans="1:4">
-      <c r="A381" t="s">
-        <v>87</v>
-      </c>
-      <c r="B381" t="s">
-        <v>33</v>
-      </c>
-      <c r="C381" t="s">
-        <v>37</v>
-      </c>
-      <c r="D381">
-        <v>38</v>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -8021,7 +2551,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>91</v>
+        <v>46</v>
       </c>
       <c r="B2">
         <v>85</v>
@@ -8101,7 +2631,7 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>92</v>
+        <v>47</v>
       </c>
       <c r="B3">
         <v>78</v>
@@ -8181,7 +2711,7 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="B4">
         <v>71</v>
@@ -8261,7 +2791,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>94</v>
+        <v>49</v>
       </c>
       <c r="B5">
         <v>65</v>
@@ -8341,7 +2871,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>95</v>
+        <v>50</v>
       </c>
       <c r="B6">
         <v>60</v>
@@ -8421,7 +2951,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="B7">
         <v>57</v>
@@ -8501,7 +3031,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>97</v>
+        <v>52</v>
       </c>
       <c r="B8">
         <v>54</v>
@@ -8581,7 +3111,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>98</v>
+        <v>53</v>
       </c>
       <c r="B9">
         <v>53</v>
@@ -8661,7 +3191,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>99</v>
+        <v>54</v>
       </c>
       <c r="B10">
         <v>53</v>
@@ -8741,7 +3271,7 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="B11">
         <v>52</v>
@@ -8821,7 +3351,7 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="B12">
         <v>52</v>
@@ -8901,7 +3431,7 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B13">
         <v>49</v>
@@ -8981,7 +3511,7 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>103</v>
+        <v>58</v>
       </c>
       <c r="B14">
         <v>49</v>
@@ -9061,7 +3591,7 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>104</v>
+        <v>59</v>
       </c>
       <c r="B15">
         <v>47</v>
@@ -9141,7 +3671,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" t="s">
-        <v>105</v>
+        <v>60</v>
       </c>
       <c r="B16">
         <v>45</v>
@@ -9221,7 +3751,7 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>61</v>
       </c>
       <c r="B17">
         <v>44</v>
@@ -9301,7 +3831,7 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" t="s">
-        <v>107</v>
+        <v>62</v>
       </c>
       <c r="B18">
         <v>41</v>
@@ -9381,7 +3911,7 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>63</v>
       </c>
       <c r="B19">
         <v>39</v>
@@ -9461,7 +3991,7 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" t="s">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="B20">
         <v>22</v>
@@ -9541,7 +4071,7 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" t="s">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="B21">
         <v>20</v>
@@ -9726,7 +4256,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="B2">
         <v>94</v>
@@ -9806,7 +4336,7 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="B3">
         <v>86</v>
@@ -9886,7 +4416,7 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>113</v>
+        <v>68</v>
       </c>
       <c r="B4">
         <v>72</v>
@@ -9966,7 +4496,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>114</v>
+        <v>69</v>
       </c>
       <c r="B5">
         <v>69</v>
@@ -10046,7 +4576,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>70</v>
       </c>
       <c r="B6">
         <v>60</v>
@@ -10126,7 +4656,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>116</v>
+        <v>71</v>
       </c>
       <c r="B7">
         <v>54</v>
@@ -10206,7 +4736,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>117</v>
+        <v>72</v>
       </c>
       <c r="B8">
         <v>51</v>
@@ -10286,7 +4816,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>73</v>
       </c>
       <c r="B9">
         <v>50</v>
@@ -10366,7 +4896,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>119</v>
+        <v>74</v>
       </c>
       <c r="B10">
         <v>49</v>
@@ -10446,7 +4976,7 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>120</v>
+        <v>75</v>
       </c>
       <c r="B11">
         <v>46</v>
@@ -10526,7 +5056,7 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>121</v>
+        <v>76</v>
       </c>
       <c r="B12">
         <v>46</v>
@@ -10606,7 +5136,7 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="B13">
         <v>45</v>
@@ -10686,7 +5216,7 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>123</v>
+        <v>78</v>
       </c>
       <c r="B14">
         <v>43</v>
@@ -10766,7 +5296,7 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>124</v>
+        <v>79</v>
       </c>
       <c r="B15">
         <v>43</v>
@@ -10846,7 +5376,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" t="s">
-        <v>125</v>
+        <v>80</v>
       </c>
       <c r="B16">
         <v>43</v>
@@ -10926,7 +5456,7 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" t="s">
-        <v>126</v>
+        <v>81</v>
       </c>
       <c r="B17">
         <v>42</v>
@@ -11006,7 +5536,7 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" t="s">
-        <v>127</v>
+        <v>82</v>
       </c>
       <c r="B18">
         <v>42</v>
@@ -11086,7 +5616,7 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>83</v>
       </c>
       <c r="B19">
         <v>42</v>
@@ -11166,7 +5696,7 @@
     </row>
     <row r="20" spans="1:26">
       <c r="A20" t="s">
-        <v>129</v>
+        <v>84</v>
       </c>
       <c r="B20">
         <v>41</v>
@@ -11246,7 +5776,7 @@
     </row>
     <row r="21" spans="1:26">
       <c r="A21" t="s">
-        <v>130</v>
+        <v>85</v>
       </c>
       <c r="B21">
         <v>29</v>
@@ -11431,7 +5961,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>131</v>
+        <v>86</v>
       </c>
       <c r="B2">
         <v>89</v>
@@ -11511,7 +6041,7 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>132</v>
+        <v>87</v>
       </c>
       <c r="B3">
         <v>73</v>
@@ -11591,7 +6121,7 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>133</v>
+        <v>88</v>
       </c>
       <c r="B4">
         <v>65</v>
@@ -11671,7 +6201,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>134</v>
+        <v>89</v>
       </c>
       <c r="B5">
         <v>62</v>
@@ -11751,7 +6281,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="B6">
         <v>61</v>
@@ -11831,7 +6361,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>136</v>
+        <v>91</v>
       </c>
       <c r="B7">
         <v>59</v>
@@ -11911,7 +6441,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>137</v>
+        <v>92</v>
       </c>
       <c r="B8">
         <v>47</v>
@@ -11991,7 +6521,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="B9">
         <v>44</v>
@@ -12071,7 +6601,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>139</v>
+        <v>94</v>
       </c>
       <c r="B10">
         <v>43</v>
@@ -12151,7 +6681,7 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>140</v>
+        <v>95</v>
       </c>
       <c r="B11">
         <v>40</v>
@@ -12231,7 +6761,7 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>141</v>
+        <v>96</v>
       </c>
       <c r="B12">
         <v>39</v>
@@ -12311,7 +6841,7 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>142</v>
+        <v>97</v>
       </c>
       <c r="B13">
         <v>38</v>
@@ -12391,7 +6921,7 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>143</v>
+        <v>98</v>
       </c>
       <c r="B14">
         <v>38</v>
@@ -12471,7 +7001,7 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>144</v>
+        <v>99</v>
       </c>
       <c r="B15">
         <v>32</v>
@@ -12551,7 +7081,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="B16">
         <v>32</v>
@@ -12631,7 +7161,7 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" t="s">
-        <v>146</v>
+        <v>101</v>
       </c>
       <c r="B17">
         <v>29</v>
@@ -12711,7 +7241,7 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="B18">
         <v>26</v>
@@ -12791,7 +7321,7 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" t="s">
-        <v>148</v>
+        <v>103</v>
       </c>
       <c r="B19">
         <v>26</v>
@@ -12976,7 +7506,7 @@
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>149</v>
+        <v>104</v>
       </c>
       <c r="B2">
         <v>76</v>
@@ -13056,7 +7586,7 @@
     </row>
     <row r="3" spans="1:26">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>105</v>
       </c>
       <c r="B3">
         <v>70</v>
@@ -13136,7 +7666,7 @@
     </row>
     <row r="4" spans="1:26">
       <c r="A4" t="s">
-        <v>151</v>
+        <v>106</v>
       </c>
       <c r="B4">
         <v>61</v>
@@ -13216,7 +7746,7 @@
     </row>
     <row r="5" spans="1:26">
       <c r="A5" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="B5">
         <v>60</v>
@@ -13296,7 +7826,7 @@
     </row>
     <row r="6" spans="1:26">
       <c r="A6" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="B6">
         <v>59</v>
@@ -13376,7 +7906,7 @@
     </row>
     <row r="7" spans="1:26">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>109</v>
       </c>
       <c r="B7">
         <v>59</v>
@@ -13456,7 +7986,7 @@
     </row>
     <row r="8" spans="1:26">
       <c r="A8" t="s">
-        <v>155</v>
+        <v>110</v>
       </c>
       <c r="B8">
         <v>54</v>
@@ -13536,7 +8066,7 @@
     </row>
     <row r="9" spans="1:26">
       <c r="A9" t="s">
-        <v>156</v>
+        <v>111</v>
       </c>
       <c r="B9">
         <v>53</v>
@@ -13616,7 +8146,7 @@
     </row>
     <row r="10" spans="1:26">
       <c r="A10" t="s">
-        <v>157</v>
+        <v>112</v>
       </c>
       <c r="B10">
         <v>45</v>
@@ -13696,7 +8226,7 @@
     </row>
     <row r="11" spans="1:26">
       <c r="A11" t="s">
-        <v>158</v>
+        <v>113</v>
       </c>
       <c r="B11">
         <v>44</v>
@@ -13776,7 +8306,7 @@
     </row>
     <row r="12" spans="1:26">
       <c r="A12" t="s">
-        <v>159</v>
+        <v>114</v>
       </c>
       <c r="B12">
         <v>44</v>
@@ -13856,7 +8386,7 @@
     </row>
     <row r="13" spans="1:26">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>115</v>
       </c>
       <c r="B13">
         <v>39</v>
@@ -13936,7 +8466,7 @@
     </row>
     <row r="14" spans="1:26">
       <c r="A14" t="s">
-        <v>161</v>
+        <v>116</v>
       </c>
       <c r="B14">
         <v>36</v>
@@ -14016,7 +8546,7 @@
     </row>
     <row r="15" spans="1:26">
       <c r="A15" t="s">
-        <v>162</v>
+        <v>117</v>
       </c>
       <c r="B15">
         <v>35</v>
@@ -14096,7 +8626,7 @@
     </row>
     <row r="16" spans="1:26">
       <c r="A16" t="s">
-        <v>163</v>
+        <v>118</v>
       </c>
       <c r="B16">
         <v>34</v>
@@ -14176,7 +8706,7 @@
     </row>
     <row r="17" spans="1:26">
       <c r="A17" t="s">
-        <v>164</v>
+        <v>119</v>
       </c>
       <c r="B17">
         <v>32</v>
@@ -14256,7 +8786,7 @@
     </row>
     <row r="18" spans="1:26">
       <c r="A18" t="s">
-        <v>165</v>
+        <v>120</v>
       </c>
       <c r="B18">
         <v>23</v>
@@ -14336,7 +8866,7 @@
     </row>
     <row r="19" spans="1:26">
       <c r="A19" t="s">
-        <v>166</v>
+        <v>121</v>
       </c>
       <c r="B19">
         <v>17</v>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J1"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,162 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:19</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Argentina - Francia</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:19</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Italia - Stati Uniti</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16/06/2026 17:19</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Brasile - Giappone</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
         </is>
       </c>
     </row>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 17:19</t>
+          <t>16/06/2026 17:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -540,7 +540,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/06/2026 17:19</t>
+          <t>16/06/2026 17:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -592,7 +592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16/06/2026 17:19</t>
+          <t>16/06/2026 17:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,156 +483,52 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FIFA World Cup</t>
+          <t>Palinsesto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 17:22</t>
+          <t>16/06/2026 19:58</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina - Francia</t>
+          <t>Nessun match in palinsesto dal provider reale per oggi</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>16/06/2026 17:22</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Italia - Stati Uniti</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>16/06/2026 17:22</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Brasile - Giappone</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 19:58</t>
+          <t>16/06/2026 20:14</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nessun match in palinsesto dal provider reale per oggi</t>
+          <t>Nessun match in palinsesto nei prossimi 4 giorni</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,52 +483,156 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Palinsesto</t>
+          <t>FIFA World Cup</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 20:14</t>
+          <t>16/06/2026 20:24</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Nessun match in palinsesto nei prossimi 4 giorni</t>
+          <t>Germania - Spagna</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:24</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Francia - Portogallo</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>16/06/2026 20:24</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Italia - Argentina</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
         </is>
       </c>
     </row>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J4"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -488,12 +488,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 20:24</t>
+          <t>16/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Germania - Spagna</t>
+          <t>Iraq - Norway</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -540,12 +540,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16/06/2026 20:24</t>
+          <t>17/06/2026 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Francia - Portogallo</t>
+          <t>Argentina - Algeria</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -592,12 +592,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>16/06/2026 20:24</t>
+          <t>17/06/2026 04:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Italia - Argentina</t>
+          <t>Austria - Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -631,6 +631,734 @@
         </is>
       </c>
       <c r="J4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17/06/2026 17:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Portugal - Congo DR</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>17/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>England - Croatia</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>17/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ghana - Panama</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18/06/2026 02:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Uzbekistan - Colombia</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>18/06/2026 16:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Czechia - South Africa</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18/06/2026 19:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Switzerland - Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18/06/2026 22:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Canada - Qatar</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19/06/2026 01:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Mexico - South Korea</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19/06/2026 19:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>United States - Australia</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19/06/2026 22:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Scotland - Morocco</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>20/06/2026 00:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Brazil - Haiti</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>20/06/2026 03:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Turkey - Paraguay</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>20/06/2026 17:00</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Netherlands - Sweden</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>20/06/2026 20:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Germany - Ivory Coast</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
         <is>
           <t>In elaborazione</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:Q17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,37 +446,72 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Punti_Casa</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Punti_Trasferta</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Casa</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Trasferta</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Risultato_Esatto</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Doppia_Chance</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>U/O_1.5</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>U/O_2.5</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>U/O_3.5</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>DC+U/O2.5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Corner_1X2</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Odds_1X2</t>
         </is>
       </c>
     </row>
@@ -488,33 +523,25 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>16/06/2026 22:00</t>
+          <t>17/06/2026 03:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Iraq - Norway</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Argentina - Algeria</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -529,6 +556,41 @@
       <c r="J2" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -540,33 +602,25 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/06/2026 01:00</t>
+          <t>17/06/2026 06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Argentina - Algeria</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Austria - Jordan</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -581,6 +635,41 @@
       <c r="J3" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -592,33 +681,25 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17/06/2026 04:00</t>
+          <t>17/06/2026 19:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austria - Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Portugal - Congo DR</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -633,6 +714,41 @@
       <c r="J4" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -644,33 +760,25 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/06/2026 17:00</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Portugal - Congo DR</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>England - Croatia</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -685,6 +793,41 @@
       <c r="J5" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -696,33 +839,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>17/06/2026 20:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Ghana - Panama</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -737,6 +872,41 @@
       <c r="J6" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -748,33 +918,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>17/06/2026 23:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Uzbekistan - Colombia</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -789,6 +951,41 @@
       <c r="J7" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -800,33 +997,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18/06/2026 02:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Czechia - South Africa</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -841,6 +1030,41 @@
       <c r="J8" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -852,33 +1076,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18/06/2026 16:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Switzerland - Bosnia-Herzegovina</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -893,6 +1109,41 @@
       <c r="J9" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -904,33 +1155,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>18/06/2026 19:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Canada - Qatar</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -945,6 +1188,41 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -956,33 +1234,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18/06/2026 22:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Mexico - South Korea</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -997,6 +1267,41 @@
       <c r="J11" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1008,33 +1313,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19/06/2026 01:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>United States - Australia</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1049,6 +1346,41 @@
       <c r="J12" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1060,33 +1392,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19/06/2026 19:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Scotland - Morocco</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>1</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1101,6 +1425,41 @@
       <c r="J13" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1112,33 +1471,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>19/06/2026 22:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Brazil - Haiti</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1153,6 +1504,41 @@
       <c r="J14" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1164,33 +1550,25 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/06/2026 00:30</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Turkey - Paraguay</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1205,6 +1583,41 @@
       <c r="J15" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1216,33 +1629,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20/06/2026 03:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Netherlands - Sweden</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>3</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1257,6 +1662,41 @@
       <c r="J16" t="inlineStr">
         <is>
           <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>
@@ -1268,33 +1708,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20/06/2026 17:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
+          <t>Germany - Ivory Coast</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>3</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1311,56 +1743,39 @@
           <t>In elaborazione</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>20/06/2026 20:00</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Germany - Ivory Coast</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
         </is>
       </c>
     </row>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q17"/>
+  <dimension ref="A1:Q19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 03:00</t>
+          <t>17/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Argentina - Algeria</t>
+          <t>England - Croatia</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -538,10 +538,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -585,7 +585,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -602,12 +602,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>17/06/2026 06:00</t>
+          <t>18/06/2026 01:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Austria - Jordan</t>
+          <t>Ghana - Panama</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -617,10 +617,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -664,7 +664,7 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -681,12 +681,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>17/06/2026 19:00</t>
+          <t>18/06/2026 04:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Portugal - Congo DR</t>
+          <t>Uzbekistan - Colombia</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -696,10 +696,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -743,7 +743,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -775,10 +775,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -822,7 +822,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -839,25 +839,25 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -918,25 +918,25 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -980,7 +980,7 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -997,25 +997,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1076,25 +1076,25 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
@@ -1155,25 +1155,25 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -1234,25 +1234,25 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -1296,7 +1296,7 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
@@ -1313,25 +1313,25 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H12" t="inlineStr">
         <is>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1392,25 +1392,25 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>3</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H13" t="inlineStr">
         <is>
@@ -1454,7 +1454,7 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
@@ -1471,25 +1471,25 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H14" t="inlineStr">
         <is>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1565,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H15" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -1629,25 +1629,25 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D16" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" t="n">
         <v>1</v>
       </c>
-      <c r="E16" t="n">
-        <v>3</v>
-      </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Non disponibile</t>
+          <t>In elaborazione</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -1708,25 +1708,25 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="H17" t="inlineStr">
         <is>
@@ -1770,10 +1770,168 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
           <t>Non disponibile</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr">
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>21/06/2026 21:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Belgium - Iran</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G18" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Uruguay - Cape Verde Islands</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>1</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G19" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -523,12 +523,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>17/06/2026 22:00</t>
+          <t>18/06/2026 18:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>England - Croatia</t>
+          <t>Czechia - South Africa</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -602,19 +602,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 01:00</t>
+          <t>18/06/2026 21:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ghana - Panama</t>
+          <t>Switzerland - Bosnia-Herzegovina</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -681,19 +681,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>18/06/2026 04:00</t>
+          <t>19/06/2026 00:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Uzbekistan - Colombia</t>
+          <t>Canada - Qatar</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -760,19 +760,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 03:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>Mexico - South Korea</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -839,19 +839,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -918,16 +918,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
@@ -997,19 +997,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1076,19 +1076,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1155,19 +1155,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D10" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
         <v>3</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1234,19 +1234,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1392,19 +1392,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D13" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" t="n">
         <v>1</v>
-      </c>
-      <c r="E13" t="n">
-        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1471,19 +1471,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1550,19 +1550,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1629,16 +1629,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1787,19 +1787,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -1866,19 +1866,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q19"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -523,19 +523,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>18/06/2026 18:00</t>
+          <t>19/06/2026 21:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Czechia - South Africa</t>
+          <t>United States - Australia</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>
@@ -602,16 +602,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>18/06/2026 21:00</t>
+          <t>20/06/2026 00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Switzerland - Bosnia-Herzegovina</t>
+          <t>Scotland - Morocco</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -681,19 +681,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>19/06/2026 00:00</t>
+          <t>20/06/2026 02:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Canada - Qatar</t>
+          <t>Brazil - Haiti</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -760,19 +760,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>19/06/2026 03:00</t>
+          <t>20/06/2026 05:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Mexico - South Korea</t>
+          <t>Turkey - Paraguay</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -839,16 +839,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
         <v>3</v>
@@ -918,19 +918,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -997,16 +997,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -1076,19 +1076,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1155,19 +1155,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1234,19 +1234,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -1313,19 +1313,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1392,16 +1392,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
@@ -1471,19 +1471,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1550,19 +1550,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1629,19 +1629,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -1708,19 +1708,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -1787,19 +1787,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -1866,19 +1866,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D19" t="n">
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -1932,6 +1932,85 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>24/06/2026 01:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Panama - Croatia</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,55 +461,75 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Media_Goal_Subiti_Casa</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Media_Goal_Trasferta</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Media_Goal_Subiti_Trasferta</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Forma_Casa</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Forma_Trasferta</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Risultato_Esatto</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Doppia_Chance</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>U/O_1.5</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>U/O_2.5</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>U/O_3.5</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Goal_NoGoal</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>DC+U/O2.5</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Corner_1X2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Odds_1X2</t>
         </is>
@@ -541,28 +561,16 @@
         <v>1.2</v>
       </c>
       <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.1</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -589,6 +597,26 @@
         </is>
       </c>
       <c r="Q2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -620,28 +648,16 @@
         <v>1.2</v>
       </c>
       <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.1</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I3" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -668,6 +684,26 @@
         </is>
       </c>
       <c r="Q3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -699,28 +735,16 @@
         <v>1.2</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
         <v>1.1</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -747,6 +771,26 @@
         </is>
       </c>
       <c r="Q4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -778,28 +822,16 @@
         <v>1.2</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
         <v>1.1</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I5" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -826,6 +858,26 @@
         </is>
       </c>
       <c r="Q5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -857,28 +909,16 @@
         <v>1.2</v>
       </c>
       <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
         <v>1.1</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -905,6 +945,26 @@
         </is>
       </c>
       <c r="Q6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -936,28 +996,16 @@
         <v>1.2</v>
       </c>
       <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
         <v>1.1</v>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I7" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -984,6 +1032,26 @@
         </is>
       </c>
       <c r="Q7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1015,28 +1083,16 @@
         <v>1.2</v>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
         <v>1.1</v>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I8" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1063,6 +1119,26 @@
         </is>
       </c>
       <c r="Q8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1094,28 +1170,16 @@
         <v>1.2</v>
       </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
         <v>1.1</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I9" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1142,6 +1206,26 @@
         </is>
       </c>
       <c r="Q9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1173,28 +1257,16 @@
         <v>1.2</v>
       </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
         <v>1.1</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1221,6 +1293,26 @@
         </is>
       </c>
       <c r="Q10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1252,28 +1344,16 @@
         <v>1.2</v>
       </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.1</v>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I11" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1300,6 +1380,26 @@
         </is>
       </c>
       <c r="Q11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1331,28 +1431,16 @@
         <v>1.2</v>
       </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
         <v>1.1</v>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I12" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1379,6 +1467,26 @@
         </is>
       </c>
       <c r="Q12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1410,28 +1518,16 @@
         <v>1.2</v>
       </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
         <v>1.1</v>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1458,6 +1554,26 @@
         </is>
       </c>
       <c r="Q13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1489,28 +1605,16 @@
         <v>1.2</v>
       </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
         <v>1.1</v>
       </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1537,6 +1641,26 @@
         </is>
       </c>
       <c r="Q14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1568,28 +1692,16 @@
         <v>1.2</v>
       </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
         <v>1.1</v>
       </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I15" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1616,6 +1728,26 @@
         </is>
       </c>
       <c r="Q15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1647,28 +1779,16 @@
         <v>1.2</v>
       </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
         <v>1.1</v>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I16" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1695,6 +1815,26 @@
         </is>
       </c>
       <c r="Q16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1726,28 +1866,16 @@
         <v>1.2</v>
       </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
         <v>1.1</v>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I17" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1774,6 +1902,26 @@
         </is>
       </c>
       <c r="Q17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1805,28 +1953,16 @@
         <v>1.2</v>
       </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
         <v>1.1</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I18" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1853,6 +1989,26 @@
         </is>
       </c>
       <c r="Q18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1884,28 +2040,16 @@
         <v>1.2</v>
       </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
         <v>1.1</v>
       </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -1932,6 +2076,26 @@
         </is>
       </c>
       <c r="Q19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
@@ -1963,28 +2127,16 @@
         <v>1.2</v>
       </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
         <v>1.1</v>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
+      <c r="I20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -2011,6 +2163,26 @@
         </is>
       </c>
       <c r="Q20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,16 +543,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>19/06/2026 21:00</t>
+          <t>20/06/2026 19:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>United States - Australia</t>
+          <t>Netherlands - Sweden</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -630,19 +630,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20/06/2026 00:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Scotland - Morocco</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -717,16 +717,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>20/06/2026 02:30</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Brazil - Haiti</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
@@ -804,19 +804,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>20/06/2026 05:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Turkey - Paraguay</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -891,19 +891,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -978,19 +978,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1065,19 +1065,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1152,16 +1152,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
@@ -1239,19 +1239,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1326,19 +1326,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -1413,19 +1413,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1500,19 +1500,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1761,16 +1761,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -1848,19 +1848,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -1935,19 +1935,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2109,16 +2109,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
@@ -2183,6 +2183,93 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>25/06/2026 00:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Scotland - Brazil</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>3</v>
+      </c>
+      <c r="E21" t="n">
+        <v>4</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:U20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,16 +543,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/06/2026 19:00</t>
+          <t>20/06/2026 22:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Netherlands - Sweden</t>
+          <t>Germany - Ivory Coast</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" t="n">
         <v>3</v>
@@ -630,19 +630,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -717,19 +717,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -804,16 +804,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
@@ -891,12 +891,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1152,19 +1152,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1239,19 +1239,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>3</v>
       </c>
       <c r="E10" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1413,16 +1413,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1500,16 +1500,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1761,19 +1761,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -1848,19 +1848,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -1940,14 +1940,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E18" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2114,14 +2114,14 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
         <v>4</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
@@ -2183,93 +2183,6 @@
         </is>
       </c>
       <c r="U20" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>25/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Scotland - Brazil</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>3</v>
-      </c>
-      <c r="E21" t="n">
-        <v>4</v>
-      </c>
-      <c r="F21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G21" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I21" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -552,10 +552,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U20"/>
+  <dimension ref="A1:U19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,19 +543,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20/06/2026 22:00</t>
+          <t>21/06/2026 02:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Germany - Ivory Coast</t>
+          <t>Ecuador - Curaçao</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>1.2</v>
@@ -630,19 +630,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>21/06/2026 06:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Tunisia - Japan</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -717,16 +717,16 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>21/06/2026 18:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Spain - Saudi Arabia</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>21/06/2026 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Belgium - Iran</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -891,12 +891,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>22/06/2026 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Uruguay - Cape Verde Islands</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -978,12 +978,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>22/06/2026 03:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>New Zealand - Egypt</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1065,19 +1065,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>22/06/2026 19:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Argentina - Austria</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1152,19 +1152,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>22/06/2026 23:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>France - Iraq</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>3</v>
       </c>
       <c r="E9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1239,12 +1239,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>23/06/2026 02:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>Norway - Senegal</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1326,16 +1326,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>23/06/2026 05:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Jordan - Algeria</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -1413,16 +1413,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>23/06/2026 19:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Portugal - Uzbekistan</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -1500,19 +1500,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>23/06/2026 22:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>England - Ghana</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1761,19 +1761,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -1853,14 +1853,14 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -1935,19 +1935,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2027,14 +2027,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
         <v>4</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2096,93 +2096,6 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>25/06/2026 00:00</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Scotland - Brazil</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>3</v>
-      </c>
-      <c r="E20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G20" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I20" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U19"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,12 +543,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21/06/2026 02:00</t>
+          <t>24/06/2026 01:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Ecuador - Curaçao</t>
+          <t>Panama - Croatia</t>
         </is>
       </c>
       <c r="D2" t="n">
@@ -630,16 +630,16 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21/06/2026 06:00</t>
+          <t>24/06/2026 04:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tunisia - Japan</t>
+          <t>Colombia - Congo DR</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
@@ -717,19 +717,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>21/06/2026 18:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Spain - Saudi Arabia</t>
+          <t>Switzerland - Canada</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -804,12 +804,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>21/06/2026 21:00</t>
+          <t>24/06/2026 21:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Belgium - Iran</t>
+          <t>Bosnia-Herzegovina - Qatar</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -891,19 +891,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>22/06/2026 00:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uruguay - Cape Verde Islands</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -978,19 +978,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>22/06/2026 03:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New Zealand - Egypt</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1065,19 +1065,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22/06/2026 19:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Argentina - Austria</t>
+          <t>Czechia - Mexico</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1152,19 +1152,19 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22/06/2026 23:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>France - Iraq</t>
+          <t>South Africa - South Korea</t>
         </is>
       </c>
       <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
         <v>3</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0</v>
       </c>
       <c r="F9" t="n">
         <v>1.2</v>
@@ -1239,19 +1239,19 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23/06/2026 02:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Norway - Senegal</t>
+          <t>Ecuador - Germany</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F10" t="n">
         <v>1.2</v>
@@ -1326,19 +1326,19 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23/06/2026 05:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Jordan - Algeria</t>
+          <t>Curaçao - Ivory Coast</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F11" t="n">
         <v>1.2</v>
@@ -1413,19 +1413,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>23/06/2026 19:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Portugal - Uzbekistan</t>
+          <t>Tunisia - Netherlands</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1500,16 +1500,16 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>23/06/2026 22:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>England - Ghana</t>
+          <t>Japan - Sweden</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E13" t="n">
         <v>3</v>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Turkey - United States</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Paraguay - Australia</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>3</v>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1761,19 +1761,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Norway - France</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -1848,19 +1848,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>Senegal - Iraq</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -1935,19 +1935,19 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Uruguay - Spain</t>
         </is>
       </c>
       <c r="D18" t="n">
+        <v>2</v>
+      </c>
+      <c r="E18" t="n">
         <v>4</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0</v>
       </c>
       <c r="F18" t="n">
         <v>1.2</v>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Scotland - Brazil</t>
+          <t>Cape Verde Islands - Saudi Arabia</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2096,6 +2096,528 @@
         </is>
       </c>
       <c r="U19" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>27/06/2026 05:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>New Zealand - Belgium</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>2</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>27/06/2026 05:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Egypt - Iran</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>4</v>
+      </c>
+      <c r="E21" t="n">
+        <v>2</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I21" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>27/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Panama - England</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>4</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I22" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>27/06/2026 23:00</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Croatia - Ghana</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="n">
+        <v>4</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I23" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>28/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Colombia - Portugal</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>3</v>
+      </c>
+      <c r="E24" t="n">
+        <v>4</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I24" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Non disponibile</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>FIFA World Cup</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>28/06/2026 01:30</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Congo DR - Uzbekistan</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="I25" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>In elaborazione</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>

--- a/Database_App_Betting.xlsx
+++ b/Database_App_Betting.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -543,16 +543,16 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24/06/2026 01:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Panama - Croatia</t>
+          <t>Morocco - Haiti</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -630,19 +630,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24/06/2026 04:00</t>
+          <t>25/06/2026 00:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Colombia - Congo DR</t>
+          <t>Scotland - Brazil</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>3</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" t="n">
         <v>1.2</v>
@@ -717,19 +717,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Switzerland - Canada</t>
+          <t>Czechia - Mexico</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F4" t="n">
         <v>1.2</v>
@@ -804,19 +804,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24/06/2026 21:00</t>
+          <t>25/06/2026 03:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Bosnia-Herzegovina - Qatar</t>
+          <t>South Africa - South Korea</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>1</v>
       </c>
       <c r="E5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F5" t="n">
         <v>1.2</v>
@@ -891,19 +891,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Morocco - Haiti</t>
+          <t>Ecuador - Germany</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="F6" t="n">
         <v>1.2</v>
@@ -978,19 +978,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25/06/2026 00:00</t>
+          <t>25/06/2026 22:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Scotland - Brazil</t>
+          <t>Curaçao - Ivory Coast</t>
         </is>
       </c>
       <c r="D7" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
         <v>3</v>
-      </c>
-      <c r="E7" t="n">
-        <v>4</v>
       </c>
       <c r="F7" t="n">
         <v>1.2</v>
@@ -1065,19 +1065,19 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>25/06/2026 03:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Czechia - Mexico</t>
+          <t>Tunisia - Netherlands</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F8" t="n">
         <v>1.2</v>
@@ -1152,16 +1152,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>25/06/2026 03:00</t>
+          <t>26/06/2026 01:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>South Africa - South Korea</t>
+          <t>Japan - Sweden</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
@@ -1239,16 +1239,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>25/06/2026 22:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Ecuador - Germany</t>
+          <t>Turkey - United States</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>6</v>
@@ -1326,16 +1326,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>25/06/2026 22:00</t>
+          <t>26/06/2026 04:00</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Curaçao - Ivory Coast</t>
+          <t>Paraguay - Australia</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E11" t="n">
         <v>3</v>
@@ -1413,19 +1413,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>26/06/2026 01:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tunisia - Netherlands</t>
+          <t>Norway - France</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F12" t="n">
         <v>1.2</v>
@@ -1500,19 +1500,19 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>26/06/2026 01:00</t>
+          <t>26/06/2026 21:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Japan - Sweden</t>
+          <t>Senegal - Iraq</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F13" t="n">
         <v>1.2</v>
@@ -1587,19 +1587,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Turkey - United States</t>
+          <t>Uruguay - Spain</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F14" t="n">
         <v>1.2</v>
@@ -1674,19 +1674,19 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>26/06/2026 04:00</t>
+          <t>27/06/2026 02:00</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Paraguay - Australia</t>
+          <t>Cape Verde Islands - Saudi Arabia</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F15" t="n">
         <v>1.2</v>
@@ -1761,19 +1761,19 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>26/06/2026 21:00</t>
+          <t>27/06/2026 05:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Norway - France</t>
+          <t>New Zealand - Belgium</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E16" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F16" t="n">
         <v>1.2</v>
@@ -1848,19 +1848,19 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>26/06/2026 21:00</t>
+          <t>27/06/2026 05:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Senegal - Iraq</t>
+          <t>Egypt - Iran</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F17" t="n">
         <v>1.2</v>
@@ -1935,16 +1935,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27/06/2026 02:00</t>
+          <t>27/06/2026 23:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Uruguay - Spain</t>
+          <t>Panama - England</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>4</v>
@@ -2022,19 +2022,19 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>27/06/2026 02:00</t>
+          <t>27/06/2026 23:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cape Verde Islands - Saudi Arabia</t>
+          <t>Croatia - Ghana</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F19" t="n">
         <v>1.2</v>
@@ -2109,19 +2109,19 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>27/06/2026 05:00</t>
+          <t>28/06/2026 01:30</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>New Zealand - Belgium</t>
+          <t>Colombia - Portugal</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F20" t="n">
         <v>1.2</v>
@@ -2196,19 +2196,19 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>27/06/2026 05:00</t>
+          <t>28/06/2026 01:30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Egypt - Iran</t>
+          <t>Congo DR - Uzbekistan</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F21" t="n">
         <v>1.2</v>
@@ -2283,19 +2283,19 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>27/06/2026 23:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Panama - England</t>
+          <t>Jordan - Argentina</t>
         </is>
       </c>
       <c r="D22" t="n">
         <v>0</v>
       </c>
       <c r="E22" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F22" t="n">
         <v>1.2</v>
@@ -2370,19 +2370,19 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>27/06/2026 23:00</t>
+          <t>28/06/2026 04:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia - Ghana</t>
+          <t>Algeria - Austria</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F23" t="n">
         <v>1.2</v>
@@ -2457,19 +2457,19 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>28/06/2026 01:30</t>
+          <t>28/06/2026 21:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Colombia - Portugal</t>
+          <t>None - None</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F24" t="n">
         <v>1.2</v>
@@ -2483,8 +2483,16 @@
       <c r="I24" t="n">
         <v>1.2</v>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>In elaborazione</t>
@@ -2531,93 +2539,6 @@
         </is>
       </c>
       <c r="U24" t="inlineStr">
-        <is>
-          <t>Non disponibile</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>FIFA World Cup</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>28/06/2026 01:30</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Congo DR - Uzbekistan</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="G25" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="I25" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>In elaborazione</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
         <is>
           <t>Non disponibile</t>
         </is>
